--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Reports\Camera Reports\Dashboard\All City Tow\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3921AF3-C1F6-423A-A691-DC9F606D16FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E324B50E-2AA4-4C4D-A1EB-2947E15C296C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="23280" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12803" uniqueCount="3799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13572" uniqueCount="4001">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -11122,12 +11122,6 @@
     <t>03/12/26 11:52 EDT</t>
   </si>
   <si>
-    <t>03/12/26 12:12 EDT</t>
-  </si>
-  <si>
-    <t>3.2mi NW of Mission KS</t>
-  </si>
-  <si>
     <t>03/12/26 12:37 EDT</t>
   </si>
   <si>
@@ -11161,30 +11155,15 @@
     <t>03/12/26 16:28 EDT</t>
   </si>
   <si>
-    <t>03/12/26 16:36 EDT</t>
-  </si>
-  <si>
     <t>03/12/26 16:38 EDT</t>
   </si>
   <si>
     <t>03/13/26 10:21 EDT</t>
   </si>
   <si>
-    <t>03/12/26 16:39 EDT</t>
-  </si>
-  <si>
-    <t>2.9mi SW of Kansas City MO</t>
-  </si>
-  <si>
     <t>03/12/26 17:00 EDT</t>
   </si>
   <si>
-    <t>03/12/26 17:14 EDT</t>
-  </si>
-  <si>
-    <t>2.4mi W of Liberty MO</t>
-  </si>
-  <si>
     <t>03/12/26 17:23 EDT</t>
   </si>
   <si>
@@ -11203,9 +11182,6 @@
     <t>03/12/26 18:20 EDT</t>
   </si>
   <si>
-    <t>03/12/26 18:21 EDT</t>
-  </si>
-  <si>
     <t>03/12/26 18:44 EDT</t>
   </si>
   <si>
@@ -11218,6 +11194,9 @@
     <t>03/12/26 18:51 EDT</t>
   </si>
   <si>
+    <t>03/16/26 12:10 EDT</t>
+  </si>
+  <si>
     <t>03/12/26 18:54 EDT</t>
   </si>
   <si>
@@ -11260,21 +11239,15 @@
     <t>5.7mi SE of Kansas City MO</t>
   </si>
   <si>
+    <t>03/16/26 12:16 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 12:18 EDT</t>
+  </si>
+  <si>
     <t>03/13/26 08:27 EDT</t>
   </si>
   <si>
-    <t>03/13/26 08:53 EDT</t>
-  </si>
-  <si>
-    <t>3.7mi SW of Joplin MO</t>
-  </si>
-  <si>
-    <t>03/13/26 08:54 EDT</t>
-  </si>
-  <si>
-    <t>4.5mi SW of Joplin MO</t>
-  </si>
-  <si>
     <t>03/13/26 09:29 EDT</t>
   </si>
   <si>
@@ -11287,13 +11260,7 @@
     <t>03/13/26 09:43 EDT</t>
   </si>
   <si>
-    <t>03/13/26 09:53 EDT</t>
-  </si>
-  <si>
-    <t>3.4mi SE of Kansas City KS</t>
-  </si>
-  <si>
-    <t>03/13/26 10:12 EDT</t>
+    <t>03/16/26 12:14 EDT</t>
   </si>
   <si>
     <t>03/13/26 10:23 EDT</t>
@@ -11305,12 +11272,6 @@
     <t>03/13/26 10:32 EDT</t>
   </si>
   <si>
-    <t>03/13/26 10:42 EDT</t>
-  </si>
-  <si>
-    <t>2.9mi S of Kansas City KS</t>
-  </si>
-  <si>
     <t>03/13/26 11:19 EDT</t>
   </si>
   <si>
@@ -11320,9 +11281,6 @@
     <t>03/13/26 11:21 EDT</t>
   </si>
   <si>
-    <t>03/13/26 12:34 EDT</t>
-  </si>
-  <si>
     <t>03/13/26 12:36 EDT</t>
   </si>
   <si>
@@ -11338,12 +11296,6 @@
     <t>3.8mi SW of Peculiar MO</t>
   </si>
   <si>
-    <t>03/13/26 14:30 EDT</t>
-  </si>
-  <si>
-    <t>2.5mi NW of Raytown MO</t>
-  </si>
-  <si>
     <t>03/13/26 15:05 EDT</t>
   </si>
   <si>
@@ -11365,9 +11317,6 @@
     <t>1.6mi E of Belton MO</t>
   </si>
   <si>
-    <t>03/13/26 16:46 EDT</t>
-  </si>
-  <si>
     <t>03/13/26 17:09 EDT</t>
   </si>
   <si>
@@ -11417,6 +11366,663 @@
   </si>
   <si>
     <t>03/14/26 08:50 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 09:42 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 09:52 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 10:00 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 10:01 EDT</t>
+  </si>
+  <si>
+    <t>0.6mi E of Richmond MO</t>
+  </si>
+  <si>
+    <t>03/14/26 10:46 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 11:29 EDT</t>
+  </si>
+  <si>
+    <t>22.8mi NW of Bolivar MO</t>
+  </si>
+  <si>
+    <t>03/14/26 11:59 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 15:14 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 19:36 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 07:23 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 09:32 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 10:33 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 15:50 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 16:55 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 18:01 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 19:33 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 22:51 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 01:03 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 05:37 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 06:08 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 06:10 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 06:14 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 06:39 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 07:51 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi NE of Grain Valley MO</t>
+  </si>
+  <si>
+    <t>03/16/26 08:59 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:20 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 09:25 EDT</t>
+  </si>
+  <si>
+    <t>0.5mi NE of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/16/26 11:23 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 12:22 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi NE of Roeland Park KS</t>
+  </si>
+  <si>
+    <t>03/16/26 13:02 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 13:13 EDT</t>
+  </si>
+  <si>
+    <t>1mi E of Hazelwood MO</t>
+  </si>
+  <si>
+    <t>03/17/26 09:22 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 13:23 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi N of Lee's Summit MO</t>
+  </si>
+  <si>
+    <t>03/17/26 09:23 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 13:54 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 14:35 EDT</t>
+  </si>
+  <si>
+    <t>5.5mi E of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/17/26 09:24 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:31 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 14:37 EDT</t>
+  </si>
+  <si>
+    <t>12.4mi SE of Nebraska City NE</t>
+  </si>
+  <si>
+    <t>03/16/26 15:07 EDT</t>
+  </si>
+  <si>
+    <t>16.6mi W of Nebraska City NE</t>
+  </si>
+  <si>
+    <t>03/16/26 15:37 EDT</t>
+  </si>
+  <si>
+    <t>8.3mi S of Lincoln NE</t>
+  </si>
+  <si>
+    <t>03/16/26 16:02 EDT</t>
+  </si>
+  <si>
+    <t>10.1mi SE of Seward NE</t>
+  </si>
+  <si>
+    <t>03/16/26 17:24 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 17:32 EDT</t>
+  </si>
+  <si>
+    <t>3.5mi NE of Kearney NE</t>
+  </si>
+  <si>
+    <t>03/16/26 17:40 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 18:13 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 18:26 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 19:02 EDT</t>
+  </si>
+  <si>
+    <t>6.7mi SW of York NE</t>
+  </si>
+  <si>
+    <t>03/16/26 20:00 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 20:15 EDT</t>
+  </si>
+  <si>
+    <t>17.2mi W of Nebraska City NE</t>
+  </si>
+  <si>
+    <t>03/16/26 20:59 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi E of Parkville MO</t>
+  </si>
+  <si>
+    <t>03/16/26 21:00 EDT</t>
+  </si>
+  <si>
+    <t>28.1mi SE of Nebraska City NE</t>
+  </si>
+  <si>
+    <t>03/16/26 22:11 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 06:19 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 06:22 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 07:35 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 08:50 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:12 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:58 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 11:53 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 09:45 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:23 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi W of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/17/26 12:32 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 13:12 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 13:31 EDT</t>
+  </si>
+  <si>
+    <t>0.3mi SW of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/18/26 09:49 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 13:36 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi E of Kansas City KS</t>
+  </si>
+  <si>
+    <t>03/17/26 14:31 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:46 EDT</t>
+  </si>
+  <si>
+    <t>3.2mi E of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/18/26 09:50 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:04 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:50 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:57 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 16:12 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 17:16 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 17:59 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 18:20 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 18:59 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 19:15 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 19:23 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi E of Belton MO</t>
+  </si>
+  <si>
+    <t>03/18/26 09:53 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 20:00 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 20:06 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 22:54 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 23:51 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 06:20 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 07:41 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 07:50 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 10:07 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 10:57 EDT</t>
+  </si>
+  <si>
+    <t>1.6mi E of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/19/26 08:03 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:35 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi SE of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/18/26 11:40 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 12:52 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 13:16 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi N of Lee's Summit MO</t>
+  </si>
+  <si>
+    <t>03/18/26 13:22 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 08:05 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 08:07 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 13:39 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 14:04 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 14:09 EDT</t>
+  </si>
+  <si>
+    <t>0.7mi W of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/18/26 14:10 EDT</t>
+  </si>
+  <si>
+    <t>1.2mi SW of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/18/26 14:11 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi SW of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/18/26 14:53 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 14:54 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 14:56 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi SE of Prairie Village KS</t>
+  </si>
+  <si>
+    <t>03/18/26 14:57 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:18 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:28 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:39 EDT</t>
+  </si>
+  <si>
+    <t>2.2mi E of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/18/26 15:44 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:50 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi SE of Lee's Summit MO</t>
+  </si>
+  <si>
+    <t>03/18/26 16:35 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 17:59 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 18:04 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi NW of Blue Springs MO</t>
+  </si>
+  <si>
+    <t>03/18/26 18:50 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 19:01 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi W of Independence MO</t>
+  </si>
+  <si>
+    <t>03/18/26 19:03 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 19:06 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 20:16 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 20:20 EDT</t>
+  </si>
+  <si>
+    <t>3mi S of Independence MO</t>
+  </si>
+  <si>
+    <t>03/18/26 20:22 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 21:05 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi S of Topeka KS</t>
+  </si>
+  <si>
+    <t>03/18/26 22:45 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 01:26 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 06:22 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 07:44 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 07:48 EDT</t>
+  </si>
+  <si>
+    <t>5.7mi N of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/19/26 08:28 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 08:32 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 07:42 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 09:37 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 09:58 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 10:05 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:07 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 13:22 EDT</t>
+  </si>
+  <si>
+    <t>3.4mi E of Prairie Village KS</t>
+  </si>
+  <si>
+    <t>03/19/26 13:58 EDT</t>
+  </si>
+  <si>
+    <t>0.5mi NW of Excelsior Springs MO</t>
+  </si>
+  <si>
+    <t>03/20/26 07:44 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 15:06 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 15:44 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 17:21 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 17:26 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 18:57 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 19:05 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 20:24 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 20:43 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 21:36 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 22:50 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 02:08 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 06:15 EDT</t>
+  </si>
+  <si>
+    <t>10.5mi S of Marshall MO</t>
+  </si>
+  <si>
+    <t>03/20/26 06:17 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 06:35 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 06:49 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 07:55 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 08:55 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 09:09 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 09:18 EDT</t>
+  </si>
+  <si>
+    <t>4.2mi NW of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/20/26 10:31 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 10:34 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 10:41 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 11:13 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:17 EDT</t>
+  </si>
+  <si>
+    <t>5.8mi NE of Pleasant Hill MO</t>
+  </si>
+  <si>
+    <t>03/20/26 13:19 EDT</t>
+  </si>
+  <si>
+    <t>18.8mi N of Bolivar MO</t>
+  </si>
+  <si>
+    <t>03/20/26 13:28 EDT</t>
+  </si>
+  <si>
+    <t>5.7mi NE of Lawrence KS</t>
+  </si>
+  <si>
+    <t>03/20/26 13:31 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi NE of Blue Springs MO</t>
+  </si>
+  <si>
+    <t>03/20/26 13:59 EDT</t>
+  </si>
+  <si>
+    <t>5mi SW of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/20/26 14:20 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 15:00 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi E of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/20/26 15:03 EDT</t>
+  </si>
+  <si>
+    <t>5.6mi NE of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/20/26 15:10 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 15:53 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 15:58 EDT</t>
   </si>
 </sst>
 </file>
@@ -11778,7 +12384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2467"/>
+  <dimension ref="A1:M2611"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -16272,19 +16878,19 @@
         <v>314</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="C156" s="3">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="D156" s="3">
-        <v>338743934</v>
+        <v>338740530</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>315</v>
+        <v>39</v>
       </c>
       <c r="G156" s="3"/>
       <c r="H156" s="3"/>
@@ -16301,19 +16907,19 @@
         <v>314</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="C157" s="3">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="D157" s="3">
-        <v>338740530</v>
+        <v>338743934</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>39</v>
+        <v>315</v>
       </c>
       <c r="G157" s="3"/>
       <c r="H157" s="3"/>
@@ -30055,19 +30661,19 @@
         <v>1052</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C625" s="3">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="D625" s="3">
-        <v>342848410</v>
+        <v>342848458</v>
       </c>
       <c r="E625" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F625" s="3" t="s">
-        <v>279</v>
+        <v>69</v>
       </c>
       <c r="G625" s="3"/>
       <c r="H625" s="3"/>
@@ -30084,19 +30690,19 @@
         <v>1052</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="C626" s="3">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D626" s="3">
-        <v>342848458</v>
+        <v>342848410</v>
       </c>
       <c r="E626" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F626" s="3" t="s">
-        <v>69</v>
+        <v>279</v>
       </c>
       <c r="G626" s="3"/>
       <c r="H626" s="3"/>
@@ -41843,19 +42449,19 @@
         <v>1699</v>
       </c>
       <c r="B1023" s="3" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C1023" s="3">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="D1023" s="3">
-        <v>346090820</v>
+        <v>346090594</v>
       </c>
       <c r="E1023" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F1023" s="3" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G1023" s="3"/>
       <c r="H1023" s="3"/>
@@ -41872,19 +42478,19 @@
         <v>1699</v>
       </c>
       <c r="B1024" s="3" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C1024" s="3">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="D1024" s="3">
-        <v>346090594</v>
+        <v>346090820</v>
       </c>
       <c r="E1024" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F1024" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G1024" s="3"/>
       <c r="H1024" s="3"/>
@@ -82269,16 +82875,16 @@
         <v>3700</v>
       </c>
       <c r="B2395" s="3" t="s">
-        <v>460</v>
+        <v>44</v>
       </c>
       <c r="C2395" s="3">
-        <v>557</v>
+        <v>480</v>
       </c>
       <c r="D2395" s="3">
-        <v>358304662</v>
+        <v>358316680</v>
       </c>
       <c r="E2395" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2395" s="3" t="s">
         <v>3701</v>
@@ -82298,16 +82904,16 @@
         <v>3702</v>
       </c>
       <c r="B2396" s="3" t="s">
-        <v>44</v>
+        <v>485</v>
       </c>
       <c r="C2396" s="3">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="D2396" s="3">
-        <v>358316680</v>
+        <v>358318349</v>
       </c>
       <c r="E2396" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F2396" s="3" t="s">
         <v>3703</v>
@@ -82327,19 +82933,19 @@
         <v>3704</v>
       </c>
       <c r="B2397" s="3" t="s">
-        <v>485</v>
+        <v>176</v>
       </c>
       <c r="C2397" s="3">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D2397" s="3">
-        <v>358318349</v>
+        <v>358340843</v>
       </c>
       <c r="E2397" s="3" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F2397" s="3" t="s">
-        <v>3705</v>
+        <v>507</v>
       </c>
       <c r="G2397" s="3"/>
       <c r="H2397" s="3"/>
@@ -82353,22 +82959,22 @@
     </row>
     <row r="2398" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2398" s="3" t="s">
-        <v>3706</v>
+        <v>3705</v>
       </c>
       <c r="B2398" s="3" t="s">
-        <v>176</v>
+        <v>1031</v>
       </c>
       <c r="C2398" s="3">
-        <v>471</v>
+        <v>558</v>
       </c>
       <c r="D2398" s="3">
-        <v>358340843</v>
+        <v>358352579</v>
       </c>
       <c r="E2398" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2398" s="3" t="s">
-        <v>507</v>
+        <v>2926</v>
       </c>
       <c r="G2398" s="3"/>
       <c r="H2398" s="3"/>
@@ -82382,22 +82988,22 @@
     </row>
     <row r="2399" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2399" s="3" t="s">
-        <v>3707</v>
+        <v>3706</v>
       </c>
       <c r="B2399" s="3" t="s">
-        <v>1031</v>
+        <v>44</v>
       </c>
       <c r="C2399" s="3">
-        <v>558</v>
+        <v>480</v>
       </c>
       <c r="D2399" s="3">
-        <v>358352579</v>
+        <v>358353608</v>
       </c>
       <c r="E2399" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2399" s="3" t="s">
-        <v>2926</v>
+        <v>257</v>
       </c>
       <c r="G2399" s="3"/>
       <c r="H2399" s="3"/>
@@ -82411,22 +83017,22 @@
     </row>
     <row r="2400" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2400" s="3" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
       <c r="B2400" s="3" t="s">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="C2400" s="3">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D2400" s="3">
-        <v>358353608</v>
+        <v>358379606</v>
       </c>
       <c r="E2400" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2400" s="3" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="G2400" s="3"/>
       <c r="H2400" s="3"/>
@@ -82440,19 +83046,19 @@
     </row>
     <row r="2401" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2401" s="3" t="s">
-        <v>3709</v>
+        <v>3708</v>
       </c>
       <c r="B2401" s="3" t="s">
-        <v>176</v>
+        <v>485</v>
       </c>
       <c r="C2401" s="3">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D2401" s="3">
-        <v>358379606</v>
+        <v>358395057</v>
       </c>
       <c r="E2401" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F2401" s="3" t="s">
         <v>279</v>
@@ -82469,7 +83075,7 @@
     </row>
     <row r="2402" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2402" s="3" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="B2402" s="3" t="s">
         <v>485</v>
@@ -82478,13 +83084,13 @@
         <v>469</v>
       </c>
       <c r="D2402" s="3">
-        <v>358395057</v>
+        <v>358407761</v>
       </c>
       <c r="E2402" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F2402" s="3" t="s">
-        <v>279</v>
+        <v>1886</v>
       </c>
       <c r="G2402" s="3"/>
       <c r="H2402" s="3"/>
@@ -82498,7 +83104,7 @@
     </row>
     <row r="2403" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2403" s="3" t="s">
-        <v>3711</v>
+        <v>3710</v>
       </c>
       <c r="B2403" s="3" t="s">
         <v>485</v>
@@ -82507,13 +83113,13 @@
         <v>469</v>
       </c>
       <c r="D2403" s="3">
-        <v>358407761</v>
+        <v>358425379</v>
       </c>
       <c r="E2403" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F2403" s="3" t="s">
-        <v>1886</v>
+        <v>1597</v>
       </c>
       <c r="G2403" s="3"/>
       <c r="H2403" s="3"/>
@@ -82527,31 +83133,37 @@
     </row>
     <row r="2404" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2404" s="3" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="B2404" s="3" t="s">
-        <v>485</v>
+        <v>644</v>
       </c>
       <c r="C2404" s="3">
-        <v>469</v>
+        <v>551</v>
       </c>
       <c r="D2404" s="3">
-        <v>358425379</v>
+        <v>358429569</v>
       </c>
       <c r="E2404" s="3" t="s">
-        <v>64</v>
+        <v>272</v>
       </c>
       <c r="F2404" s="3" t="s">
-        <v>1597</v>
-      </c>
-      <c r="G2404" s="3"/>
+        <v>380</v>
+      </c>
+      <c r="G2404" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="H2404" s="3"/>
       <c r="I2404" s="3"/>
       <c r="J2404" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2404" s="3"/>
-      <c r="L2404" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="K2404" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2404" s="3" t="s">
+        <v>3712</v>
+      </c>
       <c r="M2404" s="3"/>
     </row>
     <row r="2405" spans="1:13" x14ac:dyDescent="0.25">
@@ -82559,19 +83171,19 @@
         <v>3713</v>
       </c>
       <c r="B2405" s="3" t="s">
-        <v>644</v>
+        <v>176</v>
       </c>
       <c r="C2405" s="3">
-        <v>551</v>
+        <v>471</v>
       </c>
       <c r="D2405" s="3">
-        <v>358428180</v>
+        <v>358438128</v>
       </c>
       <c r="E2405" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2405" s="3" t="s">
-        <v>1850</v>
+        <v>279</v>
       </c>
       <c r="G2405" s="3"/>
       <c r="H2405" s="3"/>
@@ -82588,39 +83200,33 @@
         <v>3714</v>
       </c>
       <c r="B2406" s="3" t="s">
-        <v>644</v>
+        <v>485</v>
       </c>
       <c r="C2406" s="3">
-        <v>551</v>
+        <v>469</v>
       </c>
       <c r="D2406" s="3">
-        <v>358429569</v>
+        <v>358450714</v>
       </c>
       <c r="E2406" s="3" t="s">
-        <v>272</v>
+        <v>64</v>
       </c>
       <c r="F2406" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="G2406" s="3" t="s">
-        <v>261</v>
-      </c>
+        <v>3466</v>
+      </c>
+      <c r="G2406" s="3"/>
       <c r="H2406" s="3"/>
       <c r="I2406" s="3"/>
       <c r="J2406" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="K2406" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="L2406" s="3" t="s">
-        <v>3715</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="K2406" s="3"/>
+      <c r="L2406" s="3"/>
       <c r="M2406" s="3"/>
     </row>
     <row r="2407" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2407" s="3" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="B2407" s="3" t="s">
         <v>644</v>
@@ -82629,13 +83235,13 @@
         <v>551</v>
       </c>
       <c r="D2407" s="3">
-        <v>358430200</v>
+        <v>358455588</v>
       </c>
       <c r="E2407" s="3" t="s">
         <v>272</v>
       </c>
       <c r="F2407" s="3" t="s">
-        <v>3717</v>
+        <v>668</v>
       </c>
       <c r="G2407" s="3"/>
       <c r="H2407" s="3"/>
@@ -82649,22 +83255,22 @@
     </row>
     <row r="2408" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2408" s="3" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="B2408" s="3" t="s">
-        <v>176</v>
+        <v>644</v>
       </c>
       <c r="C2408" s="3">
-        <v>471</v>
+        <v>551</v>
       </c>
       <c r="D2408" s="3">
-        <v>358438128</v>
+        <v>358456113</v>
       </c>
       <c r="E2408" s="3" t="s">
-        <v>17</v>
+        <v>272</v>
       </c>
       <c r="F2408" s="3" t="s">
-        <v>279</v>
+        <v>1309</v>
       </c>
       <c r="G2408" s="3"/>
       <c r="H2408" s="3"/>
@@ -82678,22 +83284,22 @@
     </row>
     <row r="2409" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2409" s="3" t="s">
-        <v>3719</v>
+        <v>3717</v>
       </c>
       <c r="B2409" s="3" t="s">
-        <v>460</v>
+        <v>644</v>
       </c>
       <c r="C2409" s="3">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D2409" s="3">
-        <v>358444229</v>
+        <v>358456480</v>
       </c>
       <c r="E2409" s="3" t="s">
         <v>272</v>
       </c>
       <c r="F2409" s="3" t="s">
-        <v>3720</v>
+        <v>279</v>
       </c>
       <c r="G2409" s="3"/>
       <c r="H2409" s="3"/>
@@ -82707,22 +83313,22 @@
     </row>
     <row r="2410" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2410" s="3" t="s">
-        <v>3721</v>
+        <v>3718</v>
       </c>
       <c r="B2410" s="3" t="s">
-        <v>485</v>
+        <v>644</v>
       </c>
       <c r="C2410" s="3">
-        <v>469</v>
+        <v>551</v>
       </c>
       <c r="D2410" s="3">
-        <v>358450714</v>
+        <v>358456735</v>
       </c>
       <c r="E2410" s="3" t="s">
-        <v>64</v>
+        <v>272</v>
       </c>
       <c r="F2410" s="3" t="s">
-        <v>3466</v>
+        <v>39</v>
       </c>
       <c r="G2410" s="3"/>
       <c r="H2410" s="3"/>
@@ -82736,22 +83342,22 @@
     </row>
     <row r="2411" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2411" s="3" t="s">
-        <v>3722</v>
+        <v>3719</v>
       </c>
       <c r="B2411" s="3" t="s">
-        <v>644</v>
+        <v>1031</v>
       </c>
       <c r="C2411" s="3">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="D2411" s="3">
-        <v>358455588</v>
+        <v>358469391</v>
       </c>
       <c r="E2411" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2411" s="3" t="s">
-        <v>668</v>
+        <v>298</v>
       </c>
       <c r="G2411" s="3"/>
       <c r="H2411" s="3"/>
@@ -82765,36 +83371,42 @@
     </row>
     <row r="2412" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2412" s="3" t="s">
-        <v>3723</v>
+        <v>3720</v>
       </c>
       <c r="B2412" s="3" t="s">
-        <v>644</v>
+        <v>460</v>
       </c>
       <c r="C2412" s="3">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D2412" s="3">
-        <v>358456113</v>
+        <v>358476706</v>
       </c>
       <c r="E2412" s="3" t="s">
         <v>272</v>
       </c>
       <c r="F2412" s="3" t="s">
-        <v>1309</v>
-      </c>
-      <c r="G2412" s="3"/>
+        <v>2355</v>
+      </c>
+      <c r="G2412" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="H2412" s="3"/>
       <c r="I2412" s="3"/>
       <c r="J2412" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2412" s="3"/>
-      <c r="L2412" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="K2412" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2412" s="3" t="s">
+        <v>3721</v>
+      </c>
       <c r="M2412" s="3"/>
     </row>
     <row r="2413" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2413" s="3" t="s">
-        <v>3724</v>
+        <v>3722</v>
       </c>
       <c r="B2413" s="3" t="s">
         <v>644</v>
@@ -82803,13 +83415,13 @@
         <v>551</v>
       </c>
       <c r="D2413" s="3">
-        <v>358456480</v>
+        <v>358477436</v>
       </c>
       <c r="E2413" s="3" t="s">
         <v>272</v>
       </c>
       <c r="F2413" s="3" t="s">
-        <v>279</v>
+        <v>911</v>
       </c>
       <c r="G2413" s="3"/>
       <c r="H2413" s="3"/>
@@ -82823,51 +83435,57 @@
     </row>
     <row r="2414" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2414" s="3" t="s">
-        <v>3725</v>
+        <v>3723</v>
       </c>
       <c r="B2414" s="3" t="s">
-        <v>644</v>
+        <v>460</v>
       </c>
       <c r="C2414" s="3">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D2414" s="3">
-        <v>358456735</v>
+        <v>358479198</v>
       </c>
       <c r="E2414" s="3" t="s">
         <v>272</v>
       </c>
       <c r="F2414" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2414" s="3"/>
+        <v>493</v>
+      </c>
+      <c r="G2414" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="H2414" s="3"/>
       <c r="I2414" s="3"/>
       <c r="J2414" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2414" s="3"/>
-      <c r="L2414" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="K2414" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2414" s="3" t="s">
+        <v>3724</v>
+      </c>
       <c r="M2414" s="3"/>
     </row>
     <row r="2415" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2415" s="3" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
       <c r="B2415" s="3" t="s">
-        <v>1031</v>
+        <v>44</v>
       </c>
       <c r="C2415" s="3">
-        <v>558</v>
+        <v>480</v>
       </c>
       <c r="D2415" s="3">
-        <v>358469391</v>
+        <v>358480031</v>
       </c>
       <c r="E2415" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2415" s="3" t="s">
-        <v>298</v>
+        <v>1083</v>
       </c>
       <c r="G2415" s="3"/>
       <c r="H2415" s="3"/>
@@ -82881,22 +83499,22 @@
     </row>
     <row r="2416" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2416" s="3" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
       <c r="B2416" s="3" t="s">
-        <v>460</v>
+        <v>176</v>
       </c>
       <c r="C2416" s="3">
-        <v>557</v>
+        <v>471</v>
       </c>
       <c r="D2416" s="3">
-        <v>358470309</v>
+        <v>358481227</v>
       </c>
       <c r="E2416" s="3" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="F2416" s="3" t="s">
-        <v>3578</v>
+        <v>238</v>
       </c>
       <c r="G2416" s="3"/>
       <c r="H2416" s="3"/>
@@ -82910,61 +83528,59 @@
     </row>
     <row r="2417" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2417" s="3" t="s">
-        <v>3728</v>
+        <v>3727</v>
       </c>
       <c r="B2417" s="3" t="s">
-        <v>460</v>
+        <v>44</v>
       </c>
       <c r="C2417" s="3">
-        <v>557</v>
+        <v>480</v>
       </c>
       <c r="D2417" s="3">
-        <v>358476706</v>
+        <v>358495300</v>
       </c>
       <c r="E2417" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2417" s="3" t="s">
-        <v>2355</v>
-      </c>
-      <c r="G2417" s="3" t="s">
-        <v>261</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G2417" s="3"/>
       <c r="H2417" s="3"/>
       <c r="I2417" s="3"/>
       <c r="J2417" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="K2417" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="L2417" s="3" t="s">
-        <v>3729</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="K2417" s="3"/>
+      <c r="L2417" s="3"/>
       <c r="M2417" s="3"/>
     </row>
     <row r="2418" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2418" s="3" t="s">
-        <v>3730</v>
+        <v>3727</v>
       </c>
       <c r="B2418" s="3" t="s">
-        <v>644</v>
+        <v>176</v>
       </c>
       <c r="C2418" s="3">
-        <v>551</v>
+        <v>471</v>
       </c>
       <c r="D2418" s="3">
-        <v>358477436</v>
+        <v>358495009</v>
       </c>
       <c r="E2418" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2418" s="3" t="s">
-        <v>911</v>
+        <v>3728</v>
       </c>
       <c r="G2418" s="3"/>
-      <c r="H2418" s="3"/>
-      <c r="I2418" s="3"/>
+      <c r="H2418" s="3">
+        <v>42</v>
+      </c>
+      <c r="I2418" s="3">
+        <v>30</v>
+      </c>
       <c r="J2418" s="3" t="s">
         <v>19</v>
       </c>
@@ -82974,22 +83590,22 @@
     </row>
     <row r="2419" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2419" s="3" t="s">
-        <v>3731</v>
+        <v>3729</v>
       </c>
       <c r="B2419" s="3" t="s">
-        <v>460</v>
+        <v>36</v>
       </c>
       <c r="C2419" s="3">
-        <v>557</v>
+        <v>461</v>
       </c>
       <c r="D2419" s="3">
-        <v>358479198</v>
+        <v>358552211</v>
       </c>
       <c r="E2419" s="3" t="s">
-        <v>272</v>
+        <v>64</v>
       </c>
       <c r="F2419" s="3" t="s">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="G2419" s="3"/>
       <c r="H2419" s="3"/>
@@ -83003,7 +83619,7 @@
     </row>
     <row r="2420" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2420" s="3" t="s">
-        <v>3732</v>
+        <v>3730</v>
       </c>
       <c r="B2420" s="3" t="s">
         <v>44</v>
@@ -83012,13 +83628,13 @@
         <v>480</v>
       </c>
       <c r="D2420" s="3">
-        <v>358480031</v>
+        <v>358555667</v>
       </c>
       <c r="E2420" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2420" s="3" t="s">
-        <v>1083</v>
+        <v>174</v>
       </c>
       <c r="G2420" s="3"/>
       <c r="H2420" s="3"/>
@@ -83032,7 +83648,7 @@
     </row>
     <row r="2421" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2421" s="3" t="s">
-        <v>3733</v>
+        <v>3731</v>
       </c>
       <c r="B2421" s="3" t="s">
         <v>176</v>
@@ -83041,13 +83657,13 @@
         <v>471</v>
       </c>
       <c r="D2421" s="3">
-        <v>358481227</v>
+        <v>358561425</v>
       </c>
       <c r="E2421" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2421" s="3" t="s">
-        <v>238</v>
+        <v>177</v>
       </c>
       <c r="G2421" s="3"/>
       <c r="H2421" s="3"/>
@@ -83061,30 +83677,26 @@
     </row>
     <row r="2422" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2422" s="3" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="B2422" s="3" t="s">
-        <v>176</v>
+        <v>36</v>
       </c>
       <c r="C2422" s="3">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="D2422" s="3">
-        <v>358495009</v>
+        <v>358565009</v>
       </c>
       <c r="E2422" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F2422" s="3" t="s">
-        <v>3735</v>
+        <v>3733</v>
       </c>
       <c r="G2422" s="3"/>
-      <c r="H2422" s="3">
-        <v>42</v>
-      </c>
-      <c r="I2422" s="3">
-        <v>30</v>
-      </c>
+      <c r="H2422" s="3"/>
+      <c r="I2422" s="3"/>
       <c r="J2422" s="3" t="s">
         <v>19</v>
       </c>
@@ -83097,19 +83709,19 @@
         <v>3734</v>
       </c>
       <c r="B2423" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C2423" s="3">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="D2423" s="3">
-        <v>358495300</v>
+        <v>358574700</v>
       </c>
       <c r="E2423" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F2423" s="3" t="s">
-        <v>69</v>
+        <v>279</v>
       </c>
       <c r="G2423" s="3"/>
       <c r="H2423" s="3"/>
@@ -83123,22 +83735,22 @@
     </row>
     <row r="2424" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2424" s="3" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
       <c r="B2424" s="3" t="s">
-        <v>36</v>
+        <v>485</v>
       </c>
       <c r="C2424" s="3">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D2424" s="3">
-        <v>358552211</v>
+        <v>358575558</v>
       </c>
       <c r="E2424" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F2424" s="3" t="s">
-        <v>37</v>
+        <v>1292</v>
       </c>
       <c r="G2424" s="3"/>
       <c r="H2424" s="3"/>
@@ -83152,22 +83764,22 @@
     </row>
     <row r="2425" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2425" s="3" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
       <c r="B2425" s="3" t="s">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="C2425" s="3">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D2425" s="3">
-        <v>358555667</v>
+        <v>358576157</v>
       </c>
       <c r="E2425" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2425" s="3" t="s">
-        <v>174</v>
+        <v>3572</v>
       </c>
       <c r="G2425" s="3"/>
       <c r="H2425" s="3"/>
@@ -83181,51 +83793,59 @@
     </row>
     <row r="2426" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2426" s="3" t="s">
+        <v>3737</v>
+      </c>
+      <c r="B2426" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2426" s="3">
+        <v>466</v>
+      </c>
+      <c r="D2426" s="3">
+        <v>358598872</v>
+      </c>
+      <c r="E2426" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2426" s="3" t="s">
         <v>3738</v>
       </c>
-      <c r="B2426" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C2426" s="3">
-        <v>471</v>
-      </c>
-      <c r="D2426" s="3">
-        <v>358561425</v>
-      </c>
-      <c r="E2426" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2426" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G2426" s="3"/>
+      <c r="G2426" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="H2426" s="3"/>
       <c r="I2426" s="3"/>
       <c r="J2426" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2426" s="3"/>
-      <c r="L2426" s="3"/>
-      <c r="M2426" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="K2426" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2426" s="3" t="s">
+        <v>3739</v>
+      </c>
+      <c r="M2426" s="3" t="s">
+        <v>3740</v>
+      </c>
     </row>
     <row r="2427" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2427" s="3" t="s">
-        <v>3739</v>
+        <v>3741</v>
       </c>
       <c r="B2427" s="3" t="s">
-        <v>36</v>
+        <v>485</v>
       </c>
       <c r="C2427" s="3">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D2427" s="3">
-        <v>358565009</v>
+        <v>358599489</v>
       </c>
       <c r="E2427" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F2427" s="3" t="s">
-        <v>3740</v>
+        <v>3560</v>
       </c>
       <c r="G2427" s="3"/>
       <c r="H2427" s="3"/>
@@ -83239,22 +83859,22 @@
     </row>
     <row r="2428" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2428" s="3" t="s">
-        <v>3741</v>
+        <v>3742</v>
       </c>
       <c r="B2428" s="3" t="s">
-        <v>36</v>
+        <v>176</v>
       </c>
       <c r="C2428" s="3">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="D2428" s="3">
-        <v>358574700</v>
+        <v>358627438</v>
       </c>
       <c r="E2428" s="3" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F2428" s="3" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="G2428" s="3"/>
       <c r="H2428" s="3"/>
@@ -83268,7 +83888,7 @@
     </row>
     <row r="2429" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2429" s="3" t="s">
-        <v>3742</v>
+        <v>3743</v>
       </c>
       <c r="B2429" s="3" t="s">
         <v>485</v>
@@ -83277,13 +83897,13 @@
         <v>469</v>
       </c>
       <c r="D2429" s="3">
-        <v>358575558</v>
+        <v>358633776</v>
       </c>
       <c r="E2429" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F2429" s="3" t="s">
-        <v>1292</v>
+        <v>3744</v>
       </c>
       <c r="G2429" s="3"/>
       <c r="H2429" s="3"/>
@@ -83297,51 +83917,57 @@
     </row>
     <row r="2430" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2430" s="3" t="s">
-        <v>3743</v>
+        <v>3745</v>
       </c>
       <c r="B2430" s="3" t="s">
-        <v>176</v>
+        <v>644</v>
       </c>
       <c r="C2430" s="3">
-        <v>471</v>
+        <v>551</v>
       </c>
       <c r="D2430" s="3">
-        <v>358576157</v>
+        <v>358634165</v>
       </c>
       <c r="E2430" s="3" t="s">
-        <v>17</v>
+        <v>272</v>
       </c>
       <c r="F2430" s="3" t="s">
-        <v>3572</v>
-      </c>
-      <c r="G2430" s="3"/>
+        <v>470</v>
+      </c>
+      <c r="G2430" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="H2430" s="3"/>
       <c r="I2430" s="3"/>
       <c r="J2430" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2430" s="3"/>
-      <c r="L2430" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="K2430" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2430" s="3" t="s">
+        <v>3746</v>
+      </c>
       <c r="M2430" s="3"/>
     </row>
     <row r="2431" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2431" s="3" t="s">
-        <v>3744</v>
+        <v>3747</v>
       </c>
       <c r="B2431" s="3" t="s">
-        <v>463</v>
+        <v>182</v>
       </c>
       <c r="C2431" s="3">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D2431" s="3">
-        <v>358598872</v>
+        <v>358653779</v>
       </c>
       <c r="E2431" s="3" t="s">
-        <v>272</v>
+        <v>64</v>
       </c>
       <c r="F2431" s="3" t="s">
-        <v>3745</v>
+        <v>3748</v>
       </c>
       <c r="G2431" s="3"/>
       <c r="H2431" s="3"/>
@@ -83355,22 +83981,22 @@
     </row>
     <row r="2432" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2432" s="3" t="s">
-        <v>3746</v>
+        <v>3749</v>
       </c>
       <c r="B2432" s="3" t="s">
-        <v>485</v>
+        <v>176</v>
       </c>
       <c r="C2432" s="3">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D2432" s="3">
-        <v>358599489</v>
+        <v>358655844</v>
       </c>
       <c r="E2432" s="3" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F2432" s="3" t="s">
-        <v>3560</v>
+        <v>279</v>
       </c>
       <c r="G2432" s="3"/>
       <c r="H2432" s="3"/>
@@ -83384,22 +84010,22 @@
     </row>
     <row r="2433" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2433" s="3" t="s">
-        <v>3747</v>
+        <v>3750</v>
       </c>
       <c r="B2433" s="3" t="s">
-        <v>182</v>
+        <v>463</v>
       </c>
       <c r="C2433" s="3">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="D2433" s="3">
-        <v>358611737</v>
+        <v>358680753</v>
       </c>
       <c r="E2433" s="3" t="s">
-        <v>196</v>
+        <v>64</v>
       </c>
       <c r="F2433" s="3" t="s">
-        <v>3748</v>
+        <v>3751</v>
       </c>
       <c r="G2433" s="3"/>
       <c r="H2433" s="3"/>
@@ -83413,27 +84039,25 @@
     </row>
     <row r="2434" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2434" s="3" t="s">
-        <v>3749</v>
+        <v>3752</v>
       </c>
       <c r="B2434" s="3" t="s">
-        <v>182</v>
+        <v>485</v>
       </c>
       <c r="C2434" s="3">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D2434" s="3">
-        <v>358612165</v>
+        <v>358681565</v>
       </c>
       <c r="E2434" s="3" t="s">
-        <v>196</v>
+        <v>64</v>
       </c>
       <c r="F2434" s="3" t="s">
-        <v>3750</v>
+        <v>3744</v>
       </c>
       <c r="G2434" s="3"/>
-      <c r="H2434" s="3">
-        <v>52</v>
-      </c>
+      <c r="H2434" s="3"/>
       <c r="I2434" s="3"/>
       <c r="J2434" s="3" t="s">
         <v>19</v>
@@ -83444,22 +84068,22 @@
     </row>
     <row r="2435" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2435" s="3" t="s">
-        <v>3751</v>
+        <v>3753</v>
       </c>
       <c r="B2435" s="3" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C2435" s="3">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="D2435" s="3">
-        <v>358627438</v>
+        <v>358713540</v>
       </c>
       <c r="E2435" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2435" s="3" t="s">
-        <v>298</v>
+        <v>3754</v>
       </c>
       <c r="G2435" s="3"/>
       <c r="H2435" s="3"/>
@@ -83473,22 +84097,22 @@
     </row>
     <row r="2436" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2436" s="3" t="s">
-        <v>3752</v>
+        <v>3755</v>
       </c>
       <c r="B2436" s="3" t="s">
-        <v>485</v>
+        <v>176</v>
       </c>
       <c r="C2436" s="3">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D2436" s="3">
-        <v>358633776</v>
+        <v>358746375</v>
       </c>
       <c r="E2436" s="3" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F2436" s="3" t="s">
-        <v>3753</v>
+        <v>39</v>
       </c>
       <c r="G2436" s="3"/>
       <c r="H2436" s="3"/>
@@ -83502,22 +84126,22 @@
     </row>
     <row r="2437" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2437" s="3" t="s">
-        <v>3754</v>
+        <v>3756</v>
       </c>
       <c r="B2437" s="3" t="s">
-        <v>644</v>
+        <v>485</v>
       </c>
       <c r="C2437" s="3">
-        <v>551</v>
+        <v>469</v>
       </c>
       <c r="D2437" s="3">
-        <v>358634165</v>
+        <v>358767728</v>
       </c>
       <c r="E2437" s="3" t="s">
-        <v>272</v>
+        <v>64</v>
       </c>
       <c r="F2437" s="3" t="s">
-        <v>470</v>
+        <v>3757</v>
       </c>
       <c r="G2437" s="3"/>
       <c r="H2437" s="3"/>
@@ -83531,22 +84155,22 @@
     </row>
     <row r="2438" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2438" s="3" t="s">
-        <v>3755</v>
+        <v>3758</v>
       </c>
       <c r="B2438" s="3" t="s">
-        <v>644</v>
+        <v>44</v>
       </c>
       <c r="C2438" s="3">
-        <v>551</v>
+        <v>480</v>
       </c>
       <c r="D2438" s="3">
-        <v>358640001</v>
+        <v>358788477</v>
       </c>
       <c r="E2438" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2438" s="3" t="s">
-        <v>3756</v>
+        <v>31</v>
       </c>
       <c r="G2438" s="3"/>
       <c r="H2438" s="3"/>
@@ -83560,22 +84184,22 @@
     </row>
     <row r="2439" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2439" s="3" t="s">
-        <v>3757</v>
+        <v>3759</v>
       </c>
       <c r="B2439" s="3" t="s">
-        <v>195</v>
+        <v>463</v>
       </c>
       <c r="C2439" s="3">
-        <v>549</v>
+        <v>466</v>
       </c>
       <c r="D2439" s="3">
-        <v>358647718</v>
+        <v>358792760</v>
       </c>
       <c r="E2439" s="3" t="s">
-        <v>196</v>
+        <v>64</v>
       </c>
       <c r="F2439" s="3" t="s">
-        <v>1696</v>
+        <v>3760</v>
       </c>
       <c r="G2439" s="3"/>
       <c r="H2439" s="3"/>
@@ -83589,22 +84213,22 @@
     </row>
     <row r="2440" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2440" s="3" t="s">
-        <v>3758</v>
+        <v>3761</v>
       </c>
       <c r="B2440" s="3" t="s">
-        <v>182</v>
+        <v>485</v>
       </c>
       <c r="C2440" s="3">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D2440" s="3">
-        <v>358653779</v>
+        <v>358800845</v>
       </c>
       <c r="E2440" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F2440" s="3" t="s">
-        <v>3759</v>
+        <v>3762</v>
       </c>
       <c r="G2440" s="3"/>
       <c r="H2440" s="3"/>
@@ -83618,22 +84242,22 @@
     </row>
     <row r="2441" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2441" s="3" t="s">
-        <v>3760</v>
+        <v>3763</v>
       </c>
       <c r="B2441" s="3" t="s">
-        <v>176</v>
+        <v>485</v>
       </c>
       <c r="C2441" s="3">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D2441" s="3">
-        <v>358655844</v>
+        <v>358821099</v>
       </c>
       <c r="E2441" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F2441" s="3" t="s">
-        <v>279</v>
+        <v>3764</v>
       </c>
       <c r="G2441" s="3"/>
       <c r="H2441" s="3"/>
@@ -83647,22 +84271,22 @@
     </row>
     <row r="2442" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2442" s="3" t="s">
-        <v>3761</v>
+        <v>3765</v>
       </c>
       <c r="B2442" s="3" t="s">
-        <v>644</v>
+        <v>176</v>
       </c>
       <c r="C2442" s="3">
-        <v>551</v>
+        <v>471</v>
       </c>
       <c r="D2442" s="3">
-        <v>358661573</v>
+        <v>358843393</v>
       </c>
       <c r="E2442" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2442" s="3" t="s">
-        <v>3762</v>
+        <v>39</v>
       </c>
       <c r="G2442" s="3"/>
       <c r="H2442" s="3"/>
@@ -83676,22 +84300,22 @@
     </row>
     <row r="2443" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2443" s="3" t="s">
-        <v>3763</v>
+        <v>3766</v>
       </c>
       <c r="B2443" s="3" t="s">
-        <v>463</v>
+        <v>644</v>
       </c>
       <c r="C2443" s="3">
-        <v>466</v>
+        <v>551</v>
       </c>
       <c r="D2443" s="3">
-        <v>358680753</v>
+        <v>358844769</v>
       </c>
       <c r="E2443" s="3" t="s">
-        <v>64</v>
+        <v>272</v>
       </c>
       <c r="F2443" s="3" t="s">
-        <v>3764</v>
+        <v>3767</v>
       </c>
       <c r="G2443" s="3"/>
       <c r="H2443" s="3"/>
@@ -83705,22 +84329,22 @@
     </row>
     <row r="2444" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2444" s="3" t="s">
-        <v>3765</v>
+        <v>3768</v>
       </c>
       <c r="B2444" s="3" t="s">
-        <v>485</v>
+        <v>1031</v>
       </c>
       <c r="C2444" s="3">
-        <v>469</v>
+        <v>558</v>
       </c>
       <c r="D2444" s="3">
-        <v>358681565</v>
+        <v>358845439</v>
       </c>
       <c r="E2444" s="3" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F2444" s="3" t="s">
-        <v>3753</v>
+        <v>2849</v>
       </c>
       <c r="G2444" s="3"/>
       <c r="H2444" s="3"/>
@@ -83734,22 +84358,22 @@
     </row>
     <row r="2445" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2445" s="3" t="s">
-        <v>3766</v>
+        <v>3769</v>
       </c>
       <c r="B2445" s="3" t="s">
-        <v>644</v>
+        <v>485</v>
       </c>
       <c r="C2445" s="3">
-        <v>551</v>
+        <v>469</v>
       </c>
       <c r="D2445" s="3">
-        <v>358712862</v>
+        <v>358868306</v>
       </c>
       <c r="E2445" s="3" t="s">
-        <v>272</v>
+        <v>64</v>
       </c>
       <c r="F2445" s="3" t="s">
-        <v>416</v>
+        <v>3770</v>
       </c>
       <c r="G2445" s="3"/>
       <c r="H2445" s="3"/>
@@ -83763,22 +84387,22 @@
     </row>
     <row r="2446" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2446" s="3" t="s">
-        <v>3767</v>
+        <v>3771</v>
       </c>
       <c r="B2446" s="3" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C2446" s="3">
-        <v>480</v>
+        <v>548</v>
       </c>
       <c r="D2446" s="3">
-        <v>358713540</v>
+        <v>358884310</v>
       </c>
       <c r="E2446" s="3" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="F2446" s="3" t="s">
-        <v>3768</v>
+        <v>2355</v>
       </c>
       <c r="G2446" s="3"/>
       <c r="H2446" s="3"/>
@@ -83792,22 +84416,22 @@
     </row>
     <row r="2447" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2447" s="3" t="s">
-        <v>3769</v>
+        <v>3772</v>
       </c>
       <c r="B2447" s="3" t="s">
-        <v>176</v>
+        <v>485</v>
       </c>
       <c r="C2447" s="3">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D2447" s="3">
-        <v>358746375</v>
+        <v>358890114</v>
       </c>
       <c r="E2447" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F2447" s="3" t="s">
-        <v>39</v>
+        <v>3773</v>
       </c>
       <c r="G2447" s="3"/>
       <c r="H2447" s="3"/>
@@ -83821,22 +84445,22 @@
     </row>
     <row r="2448" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2448" s="3" t="s">
-        <v>3770</v>
+        <v>3774</v>
       </c>
       <c r="B2448" s="3" t="s">
-        <v>485</v>
+        <v>644</v>
       </c>
       <c r="C2448" s="3">
-        <v>469</v>
+        <v>551</v>
       </c>
       <c r="D2448" s="3">
-        <v>358767728</v>
+        <v>358892454</v>
       </c>
       <c r="E2448" s="3" t="s">
-        <v>64</v>
+        <v>272</v>
       </c>
       <c r="F2448" s="3" t="s">
-        <v>3771</v>
+        <v>3775</v>
       </c>
       <c r="G2448" s="3"/>
       <c r="H2448" s="3"/>
@@ -83850,22 +84474,22 @@
     </row>
     <row r="2449" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2449" s="3" t="s">
-        <v>3772</v>
+        <v>3776</v>
       </c>
       <c r="B2449" s="3" t="s">
-        <v>463</v>
+        <v>176</v>
       </c>
       <c r="C2449" s="3">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D2449" s="3">
-        <v>358770285</v>
+        <v>358895031</v>
       </c>
       <c r="E2449" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2449" s="3" t="s">
-        <v>3773</v>
+        <v>238</v>
       </c>
       <c r="G2449" s="3"/>
       <c r="H2449" s="3"/>
@@ -83879,22 +84503,22 @@
     </row>
     <row r="2450" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2450" s="3" t="s">
-        <v>3774</v>
+        <v>3777</v>
       </c>
       <c r="B2450" s="3" t="s">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="C2450" s="3">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D2450" s="3">
-        <v>358788477</v>
+        <v>358917683</v>
       </c>
       <c r="E2450" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2450" s="3" t="s">
-        <v>31</v>
+        <v>238</v>
       </c>
       <c r="G2450" s="3"/>
       <c r="H2450" s="3"/>
@@ -83908,22 +84532,22 @@
     </row>
     <row r="2451" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2451" s="3" t="s">
-        <v>3775</v>
+        <v>3778</v>
       </c>
       <c r="B2451" s="3" t="s">
-        <v>463</v>
+        <v>176</v>
       </c>
       <c r="C2451" s="3">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D2451" s="3">
-        <v>358792760</v>
+        <v>358927089</v>
       </c>
       <c r="E2451" s="3" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F2451" s="3" t="s">
-        <v>3776</v>
+        <v>39</v>
       </c>
       <c r="G2451" s="3"/>
       <c r="H2451" s="3"/>
@@ -83937,22 +84561,22 @@
     </row>
     <row r="2452" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2452" s="3" t="s">
-        <v>3777</v>
+        <v>3779</v>
       </c>
       <c r="B2452" s="3" t="s">
-        <v>485</v>
+        <v>176</v>
       </c>
       <c r="C2452" s="3">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D2452" s="3">
-        <v>358800845</v>
+        <v>358932610</v>
       </c>
       <c r="E2452" s="3" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F2452" s="3" t="s">
-        <v>3778</v>
+        <v>39</v>
       </c>
       <c r="G2452" s="3"/>
       <c r="H2452" s="3"/>
@@ -83966,22 +84590,22 @@
     </row>
     <row r="2453" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2453" s="3" t="s">
-        <v>3779</v>
+        <v>3780</v>
       </c>
       <c r="B2453" s="3" t="s">
-        <v>485</v>
+        <v>1031</v>
       </c>
       <c r="C2453" s="3">
-        <v>469</v>
+        <v>558</v>
       </c>
       <c r="D2453" s="3">
-        <v>358821099</v>
+        <v>358950738</v>
       </c>
       <c r="E2453" s="3" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F2453" s="3" t="s">
-        <v>3780</v>
+        <v>298</v>
       </c>
       <c r="G2453" s="3"/>
       <c r="H2453" s="3"/>
@@ -83998,16 +84622,16 @@
         <v>3781</v>
       </c>
       <c r="B2454" s="3" t="s">
-        <v>644</v>
+        <v>176</v>
       </c>
       <c r="C2454" s="3">
-        <v>551</v>
+        <v>471</v>
       </c>
       <c r="D2454" s="3">
-        <v>358833462</v>
+        <v>358951826</v>
       </c>
       <c r="E2454" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2454" s="3" t="s">
         <v>39</v>
@@ -84033,13 +84657,13 @@
         <v>471</v>
       </c>
       <c r="D2455" s="3">
-        <v>358843393</v>
+        <v>358957363</v>
       </c>
       <c r="E2455" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2455" s="3" t="s">
-        <v>39</v>
+        <v>2871</v>
       </c>
       <c r="G2455" s="3"/>
       <c r="H2455" s="3"/>
@@ -84056,19 +84680,19 @@
         <v>3783</v>
       </c>
       <c r="B2456" s="3" t="s">
-        <v>644</v>
+        <v>36</v>
       </c>
       <c r="C2456" s="3">
-        <v>551</v>
+        <v>461</v>
       </c>
       <c r="D2456" s="3">
-        <v>358844769</v>
+        <v>358958827</v>
       </c>
       <c r="E2456" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2456" s="3" t="s">
-        <v>3784</v>
+        <v>37</v>
       </c>
       <c r="G2456" s="3"/>
       <c r="H2456" s="3"/>
@@ -84082,22 +84706,22 @@
     </row>
     <row r="2457" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2457" s="3" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="B2457" s="3" t="s">
-        <v>1031</v>
+        <v>44</v>
       </c>
       <c r="C2457" s="3">
-        <v>558</v>
+        <v>480</v>
       </c>
       <c r="D2457" s="3">
-        <v>358845439</v>
+        <v>358962421</v>
       </c>
       <c r="E2457" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2457" s="3" t="s">
-        <v>2849</v>
+        <v>45</v>
       </c>
       <c r="G2457" s="3"/>
       <c r="H2457" s="3"/>
@@ -84111,22 +84735,22 @@
     </row>
     <row r="2458" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2458" s="3" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="B2458" s="3" t="s">
-        <v>485</v>
+        <v>223</v>
       </c>
       <c r="C2458" s="3">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="D2458" s="3">
-        <v>358868306</v>
+        <v>358959724</v>
       </c>
       <c r="E2458" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F2458" s="3" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="G2458" s="3"/>
       <c r="H2458" s="3"/>
@@ -84140,22 +84764,22 @@
     </row>
     <row r="2459" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2459" s="3" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="B2459" s="3" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="C2459" s="3">
-        <v>548</v>
+        <v>471</v>
       </c>
       <c r="D2459" s="3">
-        <v>358884310</v>
+        <v>358965358</v>
       </c>
       <c r="E2459" s="3" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="F2459" s="3" t="s">
-        <v>2355</v>
+        <v>39</v>
       </c>
       <c r="G2459" s="3"/>
       <c r="H2459" s="3"/>
@@ -84169,22 +84793,22 @@
     </row>
     <row r="2460" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2460" s="3" t="s">
+        <v>3788</v>
+      </c>
+      <c r="B2460" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2460" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2460" s="3">
+        <v>358971330</v>
+      </c>
+      <c r="E2460" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2460" s="3" t="s">
         <v>3789</v>
-      </c>
-      <c r="B2460" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C2460" s="3">
-        <v>469</v>
-      </c>
-      <c r="D2460" s="3">
-        <v>358890114</v>
-      </c>
-      <c r="E2460" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2460" s="3" t="s">
-        <v>3790</v>
       </c>
       <c r="G2460" s="3"/>
       <c r="H2460" s="3"/>
@@ -84198,22 +84822,22 @@
     </row>
     <row r="2461" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2461" s="3" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="B2461" s="3" t="s">
-        <v>644</v>
+        <v>44</v>
       </c>
       <c r="C2461" s="3">
-        <v>551</v>
+        <v>480</v>
       </c>
       <c r="D2461" s="3">
-        <v>358892454</v>
+        <v>358975687</v>
       </c>
       <c r="E2461" s="3" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F2461" s="3" t="s">
-        <v>3792</v>
+        <v>45</v>
       </c>
       <c r="G2461" s="3"/>
       <c r="H2461" s="3"/>
@@ -84227,7 +84851,7 @@
     </row>
     <row r="2462" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2462" s="3" t="s">
-        <v>3793</v>
+        <v>3791</v>
       </c>
       <c r="B2462" s="3" t="s">
         <v>176</v>
@@ -84236,13 +84860,13 @@
         <v>471</v>
       </c>
       <c r="D2462" s="3">
-        <v>358895031</v>
+        <v>359002926</v>
       </c>
       <c r="E2462" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2462" s="3" t="s">
-        <v>238</v>
+        <v>298</v>
       </c>
       <c r="G2462" s="3"/>
       <c r="H2462" s="3"/>
@@ -84256,7 +84880,7 @@
     </row>
     <row r="2463" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2463" s="3" t="s">
-        <v>3794</v>
+        <v>3792</v>
       </c>
       <c r="B2463" s="3" t="s">
         <v>176</v>
@@ -84265,7 +84889,7 @@
         <v>471</v>
       </c>
       <c r="D2463" s="3">
-        <v>358917683</v>
+        <v>359033169</v>
       </c>
       <c r="E2463" s="3" t="s">
         <v>17</v>
@@ -84285,7 +84909,7 @@
     </row>
     <row r="2464" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2464" s="3" t="s">
-        <v>3795</v>
+        <v>3793</v>
       </c>
       <c r="B2464" s="3" t="s">
         <v>176</v>
@@ -84294,13 +84918,13 @@
         <v>471</v>
       </c>
       <c r="D2464" s="3">
-        <v>358927089</v>
+        <v>359066669</v>
       </c>
       <c r="E2464" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2464" s="3" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="G2464" s="3"/>
       <c r="H2464" s="3"/>
@@ -84314,22 +84938,22 @@
     </row>
     <row r="2465" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2465" s="3" t="s">
-        <v>3796</v>
+        <v>3794</v>
       </c>
       <c r="B2465" s="3" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C2465" s="3">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="D2465" s="3">
-        <v>358932610</v>
+        <v>359073317</v>
       </c>
       <c r="E2465" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2465" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G2465" s="3"/>
       <c r="H2465" s="3"/>
@@ -84343,22 +84967,22 @@
     </row>
     <row r="2466" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2466" s="3" t="s">
-        <v>3797</v>
+        <v>3795</v>
       </c>
       <c r="B2466" s="3" t="s">
-        <v>1031</v>
+        <v>44</v>
       </c>
       <c r="C2466" s="3">
-        <v>558</v>
+        <v>480</v>
       </c>
       <c r="D2466" s="3">
-        <v>358950738</v>
+        <v>359077180</v>
       </c>
       <c r="E2466" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2466" s="3" t="s">
-        <v>298</v>
+        <v>934</v>
       </c>
       <c r="G2466" s="3"/>
       <c r="H2466" s="3"/>
@@ -84372,7 +84996,7 @@
     </row>
     <row r="2467" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2467" s="3" t="s">
-        <v>3798</v>
+        <v>3796</v>
       </c>
       <c r="B2467" s="3" t="s">
         <v>176</v>
@@ -84381,7 +85005,7 @@
         <v>471</v>
       </c>
       <c r="D2467" s="3">
-        <v>358951826</v>
+        <v>359103917</v>
       </c>
       <c r="E2467" s="3" t="s">
         <v>17</v>
@@ -84399,6 +85023,4266 @@
       <c r="L2467" s="3"/>
       <c r="M2467" s="3"/>
     </row>
+    <row r="2468" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2468" s="3" t="s">
+        <v>3797</v>
+      </c>
+      <c r="B2468" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2468" s="3">
+        <v>473</v>
+      </c>
+      <c r="D2468" s="3">
+        <v>359109997</v>
+      </c>
+      <c r="E2468" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2468" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2468" s="3"/>
+      <c r="H2468" s="3"/>
+      <c r="I2468" s="3"/>
+      <c r="J2468" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2468" s="3"/>
+      <c r="L2468" s="3"/>
+      <c r="M2468" s="3"/>
+    </row>
+    <row r="2469" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2469" s="3" t="s">
+        <v>3798</v>
+      </c>
+      <c r="B2469" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2469" s="3">
+        <v>558</v>
+      </c>
+      <c r="D2469" s="3">
+        <v>359116175</v>
+      </c>
+      <c r="E2469" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2469" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G2469" s="3"/>
+      <c r="H2469" s="3"/>
+      <c r="I2469" s="3"/>
+      <c r="J2469" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2469" s="3"/>
+      <c r="L2469" s="3"/>
+      <c r="M2469" s="3"/>
+    </row>
+    <row r="2470" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2470" s="3" t="s">
+        <v>3799</v>
+      </c>
+      <c r="B2470" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2470" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2470" s="3">
+        <v>359122855</v>
+      </c>
+      <c r="E2470" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2470" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2470" s="3"/>
+      <c r="H2470" s="3"/>
+      <c r="I2470" s="3"/>
+      <c r="J2470" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2470" s="3"/>
+      <c r="L2470" s="3"/>
+      <c r="M2470" s="3"/>
+    </row>
+    <row r="2471" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2471" s="3" t="s">
+        <v>3800</v>
+      </c>
+      <c r="B2471" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2471" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2471" s="3">
+        <v>359136193</v>
+      </c>
+      <c r="E2471" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2471" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2471" s="3"/>
+      <c r="H2471" s="3"/>
+      <c r="I2471" s="3"/>
+      <c r="J2471" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2471" s="3"/>
+      <c r="L2471" s="3"/>
+      <c r="M2471" s="3"/>
+    </row>
+    <row r="2472" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2472" s="3" t="s">
+        <v>3801</v>
+      </c>
+      <c r="B2472" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2472" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2472" s="3">
+        <v>359142560</v>
+      </c>
+      <c r="E2472" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2472" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2472" s="3"/>
+      <c r="H2472" s="3"/>
+      <c r="I2472" s="3"/>
+      <c r="J2472" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2472" s="3"/>
+      <c r="L2472" s="3"/>
+      <c r="M2472" s="3"/>
+    </row>
+    <row r="2473" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2473" s="3" t="s">
+        <v>3802</v>
+      </c>
+      <c r="B2473" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2473" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2473" s="3">
+        <v>359158205</v>
+      </c>
+      <c r="E2473" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2473" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="G2473" s="3"/>
+      <c r="H2473" s="3"/>
+      <c r="I2473" s="3"/>
+      <c r="J2473" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2473" s="3"/>
+      <c r="L2473" s="3"/>
+      <c r="M2473" s="3"/>
+    </row>
+    <row r="2474" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2474" s="3" t="s">
+        <v>3803</v>
+      </c>
+      <c r="B2474" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2474" s="3">
+        <v>461</v>
+      </c>
+      <c r="D2474" s="3">
+        <v>359163788</v>
+      </c>
+      <c r="E2474" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2474" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2474" s="3"/>
+      <c r="H2474" s="3"/>
+      <c r="I2474" s="3"/>
+      <c r="J2474" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2474" s="3"/>
+      <c r="L2474" s="3"/>
+      <c r="M2474" s="3"/>
+    </row>
+    <row r="2475" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2475" s="3" t="s">
+        <v>3804</v>
+      </c>
+      <c r="B2475" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2475" s="3">
+        <v>461</v>
+      </c>
+      <c r="D2475" s="3">
+        <v>359164169</v>
+      </c>
+      <c r="E2475" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2475" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2475" s="3"/>
+      <c r="H2475" s="3"/>
+      <c r="I2475" s="3"/>
+      <c r="J2475" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2475" s="3"/>
+      <c r="L2475" s="3"/>
+      <c r="M2475" s="3"/>
+    </row>
+    <row r="2476" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2476" s="3" t="s">
+        <v>3805</v>
+      </c>
+      <c r="B2476" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2476" s="3">
+        <v>536</v>
+      </c>
+      <c r="D2476" s="3">
+        <v>359164200</v>
+      </c>
+      <c r="E2476" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2476" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2476" s="3"/>
+      <c r="H2476" s="3"/>
+      <c r="I2476" s="3"/>
+      <c r="J2476" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2476" s="3"/>
+      <c r="L2476" s="3"/>
+      <c r="M2476" s="3"/>
+    </row>
+    <row r="2477" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2477" s="3" t="s">
+        <v>3806</v>
+      </c>
+      <c r="B2477" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C2477" s="3">
+        <v>555</v>
+      </c>
+      <c r="D2477" s="3">
+        <v>359169759</v>
+      </c>
+      <c r="E2477" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2477" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2477" s="3"/>
+      <c r="H2477" s="3"/>
+      <c r="I2477" s="3"/>
+      <c r="J2477" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2477" s="3"/>
+      <c r="L2477" s="3"/>
+      <c r="M2477" s="3"/>
+    </row>
+    <row r="2478" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2478" s="3" t="s">
+        <v>3807</v>
+      </c>
+      <c r="B2478" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2478" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2478" s="3">
+        <v>359193284</v>
+      </c>
+      <c r="E2478" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2478" s="3" t="s">
+        <v>3808</v>
+      </c>
+      <c r="G2478" s="3"/>
+      <c r="H2478" s="3"/>
+      <c r="I2478" s="3"/>
+      <c r="J2478" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2478" s="3"/>
+      <c r="L2478" s="3"/>
+      <c r="M2478" s="3"/>
+    </row>
+    <row r="2479" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2479" s="3" t="s">
+        <v>3809</v>
+      </c>
+      <c r="B2479" s="3" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C2479" s="3">
+        <v>537</v>
+      </c>
+      <c r="D2479" s="3">
+        <v>359218008</v>
+      </c>
+      <c r="E2479" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2479" s="3" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G2479" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2479" s="3"/>
+      <c r="I2479" s="3"/>
+      <c r="J2479" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2479" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2479" s="3" t="s">
+        <v>3810</v>
+      </c>
+      <c r="M2479" s="3"/>
+    </row>
+    <row r="2480" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2480" s="3" t="s">
+        <v>3811</v>
+      </c>
+      <c r="B2480" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2480" s="3">
+        <v>553</v>
+      </c>
+      <c r="D2480" s="3">
+        <v>359230067</v>
+      </c>
+      <c r="E2480" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2480" s="3" t="s">
+        <v>3812</v>
+      </c>
+      <c r="G2480" s="3"/>
+      <c r="H2480" s="3"/>
+      <c r="I2480" s="3"/>
+      <c r="J2480" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2480" s="3"/>
+      <c r="L2480" s="3"/>
+      <c r="M2480" s="3"/>
+    </row>
+    <row r="2481" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2481" s="3" t="s">
+        <v>3813</v>
+      </c>
+      <c r="B2481" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2481" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2481" s="3">
+        <v>359280347</v>
+      </c>
+      <c r="E2481" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2481" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2481" s="3"/>
+      <c r="H2481" s="3"/>
+      <c r="I2481" s="3"/>
+      <c r="J2481" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2481" s="3"/>
+      <c r="L2481" s="3"/>
+      <c r="M2481" s="3"/>
+    </row>
+    <row r="2482" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2482" s="3" t="s">
+        <v>3814</v>
+      </c>
+      <c r="B2482" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2482" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2482" s="3">
+        <v>359306486</v>
+      </c>
+      <c r="E2482" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2482" s="3" t="s">
+        <v>3815</v>
+      </c>
+      <c r="G2482" s="3"/>
+      <c r="H2482" s="3"/>
+      <c r="I2482" s="3"/>
+      <c r="J2482" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2482" s="3"/>
+      <c r="L2482" s="3"/>
+      <c r="M2482" s="3"/>
+    </row>
+    <row r="2483" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2483" s="3" t="s">
+        <v>3816</v>
+      </c>
+      <c r="B2483" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2483" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2483" s="3">
+        <v>359342084</v>
+      </c>
+      <c r="E2483" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2483" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2483" s="3"/>
+      <c r="H2483" s="3"/>
+      <c r="I2483" s="3"/>
+      <c r="J2483" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2483" s="3"/>
+      <c r="L2483" s="3"/>
+      <c r="M2483" s="3"/>
+    </row>
+    <row r="2484" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2484" s="3" t="s">
+        <v>3817</v>
+      </c>
+      <c r="B2484" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2484" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2484" s="3">
+        <v>359327426</v>
+      </c>
+      <c r="E2484" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2484" s="3" t="s">
+        <v>3818</v>
+      </c>
+      <c r="G2484" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2484" s="3"/>
+      <c r="I2484" s="3"/>
+      <c r="J2484" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2484" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2484" s="3" t="s">
+        <v>3819</v>
+      </c>
+      <c r="M2484" s="3"/>
+    </row>
+    <row r="2485" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2485" s="3" t="s">
+        <v>3820</v>
+      </c>
+      <c r="B2485" s="3" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C2485" s="3">
+        <v>542</v>
+      </c>
+      <c r="D2485" s="3">
+        <v>359333244</v>
+      </c>
+      <c r="E2485" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2485" s="3" t="s">
+        <v>3821</v>
+      </c>
+      <c r="G2485" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2485" s="3"/>
+      <c r="I2485" s="3"/>
+      <c r="J2485" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2485" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2485" s="3" t="s">
+        <v>3822</v>
+      </c>
+      <c r="M2485" s="3"/>
+    </row>
+    <row r="2486" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2486" s="3" t="s">
+        <v>3823</v>
+      </c>
+      <c r="B2486" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2486" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2486" s="3">
+        <v>359347123</v>
+      </c>
+      <c r="E2486" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2486" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2486" s="3"/>
+      <c r="H2486" s="3"/>
+      <c r="I2486" s="3"/>
+      <c r="J2486" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2486" s="3"/>
+      <c r="L2486" s="3"/>
+      <c r="M2486" s="3"/>
+    </row>
+    <row r="2487" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2487" s="3" t="s">
+        <v>3824</v>
+      </c>
+      <c r="B2487" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2487" s="3">
+        <v>466</v>
+      </c>
+      <c r="D2487" s="3">
+        <v>359365474</v>
+      </c>
+      <c r="E2487" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2487" s="3" t="s">
+        <v>3825</v>
+      </c>
+      <c r="G2487" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2487" s="3"/>
+      <c r="I2487" s="3"/>
+      <c r="J2487" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2487" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2487" s="3" t="s">
+        <v>3826</v>
+      </c>
+      <c r="M2487" s="3" t="s">
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2488" s="3" t="s">
+        <v>3828</v>
+      </c>
+      <c r="B2488" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2488" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2488" s="3">
+        <v>359369615</v>
+      </c>
+      <c r="E2488" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2488" s="3" t="s">
+        <v>3829</v>
+      </c>
+      <c r="G2488" s="3"/>
+      <c r="H2488" s="3"/>
+      <c r="I2488" s="3"/>
+      <c r="J2488" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2488" s="3"/>
+      <c r="L2488" s="3"/>
+      <c r="M2488" s="3"/>
+    </row>
+    <row r="2489" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2489" s="3" t="s">
+        <v>3830</v>
+      </c>
+      <c r="B2489" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2489" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2489" s="3">
+        <v>359382858</v>
+      </c>
+      <c r="E2489" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2489" s="3" t="s">
+        <v>3831</v>
+      </c>
+      <c r="G2489" s="3"/>
+      <c r="H2489" s="3"/>
+      <c r="I2489" s="3"/>
+      <c r="J2489" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2489" s="3"/>
+      <c r="L2489" s="3"/>
+      <c r="M2489" s="3"/>
+    </row>
+    <row r="2490" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2490" s="3" t="s">
+        <v>3832</v>
+      </c>
+      <c r="B2490" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2490" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2490" s="3">
+        <v>359395122</v>
+      </c>
+      <c r="E2490" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2490" s="3" t="s">
+        <v>3833</v>
+      </c>
+      <c r="G2490" s="3"/>
+      <c r="H2490" s="3"/>
+      <c r="I2490" s="3"/>
+      <c r="J2490" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2490" s="3"/>
+      <c r="L2490" s="3"/>
+      <c r="M2490" s="3"/>
+    </row>
+    <row r="2491" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2491" s="3" t="s">
+        <v>3834</v>
+      </c>
+      <c r="B2491" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2491" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2491" s="3">
+        <v>359407128</v>
+      </c>
+      <c r="E2491" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2491" s="3" t="s">
+        <v>3835</v>
+      </c>
+      <c r="G2491" s="3"/>
+      <c r="H2491" s="3"/>
+      <c r="I2491" s="3"/>
+      <c r="J2491" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2491" s="3"/>
+      <c r="L2491" s="3"/>
+      <c r="M2491" s="3"/>
+    </row>
+    <row r="2492" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2492" s="3" t="s">
+        <v>3836</v>
+      </c>
+      <c r="B2492" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2492" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2492" s="3">
+        <v>359438316</v>
+      </c>
+      <c r="E2492" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2492" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2492" s="3"/>
+      <c r="H2492" s="3"/>
+      <c r="I2492" s="3"/>
+      <c r="J2492" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2492" s="3"/>
+      <c r="L2492" s="3"/>
+      <c r="M2492" s="3"/>
+    </row>
+    <row r="2493" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2493" s="3" t="s">
+        <v>3837</v>
+      </c>
+      <c r="B2493" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2493" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2493" s="3">
+        <v>359442244</v>
+      </c>
+      <c r="E2493" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2493" s="3" t="s">
+        <v>3838</v>
+      </c>
+      <c r="G2493" s="3"/>
+      <c r="H2493" s="3"/>
+      <c r="I2493" s="3"/>
+      <c r="J2493" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2493" s="3"/>
+      <c r="L2493" s="3"/>
+      <c r="M2493" s="3"/>
+    </row>
+    <row r="2494" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2494" s="3" t="s">
+        <v>3839</v>
+      </c>
+      <c r="B2494" s="3" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C2494" s="3">
+        <v>537</v>
+      </c>
+      <c r="D2494" s="3">
+        <v>359443717</v>
+      </c>
+      <c r="E2494" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2494" s="3" t="s">
+        <v>3453</v>
+      </c>
+      <c r="G2494" s="3"/>
+      <c r="H2494" s="3"/>
+      <c r="I2494" s="3"/>
+      <c r="J2494" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2494" s="3"/>
+      <c r="L2494" s="3"/>
+      <c r="M2494" s="3"/>
+    </row>
+    <row r="2495" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2495" s="3" t="s">
+        <v>3840</v>
+      </c>
+      <c r="B2495" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2495" s="3">
+        <v>548</v>
+      </c>
+      <c r="D2495" s="3">
+        <v>359453657</v>
+      </c>
+      <c r="E2495" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2495" s="3" t="s">
+        <v>3557</v>
+      </c>
+      <c r="G2495" s="3"/>
+      <c r="H2495" s="3"/>
+      <c r="I2495" s="3"/>
+      <c r="J2495" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2495" s="3"/>
+      <c r="L2495" s="3"/>
+      <c r="M2495" s="3"/>
+    </row>
+    <row r="2496" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2496" s="3" t="s">
+        <v>3841</v>
+      </c>
+      <c r="B2496" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2496" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2496" s="3">
+        <v>359457417</v>
+      </c>
+      <c r="E2496" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2496" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2496" s="3"/>
+      <c r="H2496" s="3"/>
+      <c r="I2496" s="3"/>
+      <c r="J2496" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2496" s="3"/>
+      <c r="L2496" s="3"/>
+      <c r="M2496" s="3"/>
+    </row>
+    <row r="2497" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2497" s="3" t="s">
+        <v>3842</v>
+      </c>
+      <c r="B2497" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2497" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2497" s="3">
+        <v>359466184</v>
+      </c>
+      <c r="E2497" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2497" s="3" t="s">
+        <v>3843</v>
+      </c>
+      <c r="G2497" s="3"/>
+      <c r="H2497" s="3"/>
+      <c r="I2497" s="3"/>
+      <c r="J2497" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2497" s="3"/>
+      <c r="L2497" s="3"/>
+      <c r="M2497" s="3"/>
+    </row>
+    <row r="2498" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2498" s="3" t="s">
+        <v>3844</v>
+      </c>
+      <c r="B2498" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2498" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2498" s="3">
+        <v>359477235</v>
+      </c>
+      <c r="E2498" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2498" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2498" s="3"/>
+      <c r="H2498" s="3"/>
+      <c r="I2498" s="3"/>
+      <c r="J2498" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2498" s="3"/>
+      <c r="L2498" s="3"/>
+      <c r="M2498" s="3"/>
+    </row>
+    <row r="2499" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2499" s="3" t="s">
+        <v>3845</v>
+      </c>
+      <c r="B2499" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2499" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2499" s="3">
+        <v>359479706</v>
+      </c>
+      <c r="E2499" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2499" s="3" t="s">
+        <v>3846</v>
+      </c>
+      <c r="G2499" s="3"/>
+      <c r="H2499" s="3"/>
+      <c r="I2499" s="3"/>
+      <c r="J2499" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2499" s="3"/>
+      <c r="L2499" s="3"/>
+      <c r="M2499" s="3"/>
+    </row>
+    <row r="2500" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2500" s="3" t="s">
+        <v>3847</v>
+      </c>
+      <c r="B2500" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2500" s="3">
+        <v>536</v>
+      </c>
+      <c r="D2500" s="3">
+        <v>359485326</v>
+      </c>
+      <c r="E2500" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2500" s="3" t="s">
+        <v>3848</v>
+      </c>
+      <c r="G2500" s="3"/>
+      <c r="H2500" s="3"/>
+      <c r="I2500" s="3"/>
+      <c r="J2500" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2500" s="3"/>
+      <c r="L2500" s="3"/>
+      <c r="M2500" s="3"/>
+    </row>
+    <row r="2501" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2501" s="3" t="s">
+        <v>3849</v>
+      </c>
+      <c r="B2501" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2501" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2501" s="3">
+        <v>359485355</v>
+      </c>
+      <c r="E2501" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2501" s="3" t="s">
+        <v>3850</v>
+      </c>
+      <c r="G2501" s="3"/>
+      <c r="H2501" s="3"/>
+      <c r="I2501" s="3"/>
+      <c r="J2501" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2501" s="3"/>
+      <c r="L2501" s="3"/>
+      <c r="M2501" s="3"/>
+    </row>
+    <row r="2502" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2502" s="3" t="s">
+        <v>3851</v>
+      </c>
+      <c r="B2502" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2502" s="3">
+        <v>536</v>
+      </c>
+      <c r="D2502" s="3">
+        <v>359491624</v>
+      </c>
+      <c r="E2502" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2502" s="3" t="s">
+        <v>2434</v>
+      </c>
+      <c r="G2502" s="3"/>
+      <c r="H2502" s="3"/>
+      <c r="I2502" s="3"/>
+      <c r="J2502" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2502" s="3"/>
+      <c r="L2502" s="3"/>
+      <c r="M2502" s="3"/>
+    </row>
+    <row r="2503" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2503" s="3" t="s">
+        <v>3852</v>
+      </c>
+      <c r="B2503" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2503" s="3">
+        <v>461</v>
+      </c>
+      <c r="D2503" s="3">
+        <v>359534409</v>
+      </c>
+      <c r="E2503" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2503" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2503" s="3"/>
+      <c r="H2503" s="3"/>
+      <c r="I2503" s="3"/>
+      <c r="J2503" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2503" s="3"/>
+      <c r="L2503" s="3"/>
+      <c r="M2503" s="3"/>
+    </row>
+    <row r="2504" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2504" s="3" t="s">
+        <v>3853</v>
+      </c>
+      <c r="B2504" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2504" s="3">
+        <v>461</v>
+      </c>
+      <c r="D2504" s="3">
+        <v>359536494</v>
+      </c>
+      <c r="E2504" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2504" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2504" s="3"/>
+      <c r="H2504" s="3"/>
+      <c r="I2504" s="3"/>
+      <c r="J2504" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2504" s="3"/>
+      <c r="L2504" s="3"/>
+      <c r="M2504" s="3"/>
+    </row>
+    <row r="2505" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2505" s="3" t="s">
+        <v>3854</v>
+      </c>
+      <c r="B2505" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2505" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2505" s="3">
+        <v>359559768</v>
+      </c>
+      <c r="E2505" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2505" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2505" s="3"/>
+      <c r="H2505" s="3"/>
+      <c r="I2505" s="3"/>
+      <c r="J2505" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2505" s="3"/>
+      <c r="L2505" s="3"/>
+      <c r="M2505" s="3"/>
+    </row>
+    <row r="2506" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2506" s="3" t="s">
+        <v>3855</v>
+      </c>
+      <c r="B2506" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2506" s="3">
+        <v>548</v>
+      </c>
+      <c r="D2506" s="3">
+        <v>359593385</v>
+      </c>
+      <c r="E2506" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2506" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G2506" s="3"/>
+      <c r="H2506" s="3"/>
+      <c r="I2506" s="3"/>
+      <c r="J2506" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2506" s="3"/>
+      <c r="L2506" s="3"/>
+      <c r="M2506" s="3"/>
+    </row>
+    <row r="2507" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2507" s="3" t="s">
+        <v>3856</v>
+      </c>
+      <c r="B2507" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2507" s="3">
+        <v>558</v>
+      </c>
+      <c r="D2507" s="3">
+        <v>359602047</v>
+      </c>
+      <c r="E2507" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2507" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G2507" s="3"/>
+      <c r="H2507" s="3"/>
+      <c r="I2507" s="3"/>
+      <c r="J2507" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2507" s="3"/>
+      <c r="L2507" s="3"/>
+      <c r="M2507" s="3"/>
+    </row>
+    <row r="2508" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2508" s="3" t="s">
+        <v>3857</v>
+      </c>
+      <c r="B2508" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2508" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2508" s="3">
+        <v>359624686</v>
+      </c>
+      <c r="E2508" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2508" s="3" t="s">
+        <v>3815</v>
+      </c>
+      <c r="G2508" s="3"/>
+      <c r="H2508" s="3"/>
+      <c r="I2508" s="3"/>
+      <c r="J2508" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2508" s="3"/>
+      <c r="L2508" s="3"/>
+      <c r="M2508" s="3"/>
+    </row>
+    <row r="2509" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2509" s="3" t="s">
+        <v>3858</v>
+      </c>
+      <c r="B2509" s="3" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C2509" s="3">
+        <v>537</v>
+      </c>
+      <c r="D2509" s="3">
+        <v>359683263</v>
+      </c>
+      <c r="E2509" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2509" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="G2509" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2509" s="3"/>
+      <c r="I2509" s="3"/>
+      <c r="J2509" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2509" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2509" s="3" t="s">
+        <v>3859</v>
+      </c>
+      <c r="M2509" s="3"/>
+    </row>
+    <row r="2510" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2510" s="3" t="s">
+        <v>3860</v>
+      </c>
+      <c r="B2510" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2510" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2510" s="3">
+        <v>359698697</v>
+      </c>
+      <c r="E2510" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2510" s="3" t="s">
+        <v>3861</v>
+      </c>
+      <c r="G2510" s="3"/>
+      <c r="H2510" s="3"/>
+      <c r="I2510" s="3"/>
+      <c r="J2510" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2510" s="3"/>
+      <c r="L2510" s="3"/>
+      <c r="M2510" s="3"/>
+    </row>
+    <row r="2511" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2511" s="3" t="s">
+        <v>3862</v>
+      </c>
+      <c r="B2511" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2511" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2511" s="3">
+        <v>359702300</v>
+      </c>
+      <c r="E2511" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2511" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G2511" s="3"/>
+      <c r="H2511" s="3"/>
+      <c r="I2511" s="3"/>
+      <c r="J2511" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2511" s="3"/>
+      <c r="L2511" s="3"/>
+      <c r="M2511" s="3"/>
+    </row>
+    <row r="2512" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2512" s="3" t="s">
+        <v>3863</v>
+      </c>
+      <c r="B2512" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2512" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2512" s="3">
+        <v>359725687</v>
+      </c>
+      <c r="E2512" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2512" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2512" s="3"/>
+      <c r="H2512" s="3"/>
+      <c r="I2512" s="3"/>
+      <c r="J2512" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2512" s="3"/>
+      <c r="L2512" s="3"/>
+      <c r="M2512" s="3"/>
+    </row>
+    <row r="2513" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2513" s="3" t="s">
+        <v>3864</v>
+      </c>
+      <c r="B2513" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2513" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2513" s="3">
+        <v>359732307</v>
+      </c>
+      <c r="E2513" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2513" s="3" t="s">
+        <v>3865</v>
+      </c>
+      <c r="G2513" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2513" s="3"/>
+      <c r="I2513" s="3"/>
+      <c r="J2513" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2513" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2513" s="3" t="s">
+        <v>3866</v>
+      </c>
+      <c r="M2513" s="3"/>
+    </row>
+    <row r="2514" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2514" s="3" t="s">
+        <v>3867</v>
+      </c>
+      <c r="B2514" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2514" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2514" s="3">
+        <v>359734018</v>
+      </c>
+      <c r="E2514" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2514" s="3" t="s">
+        <v>3868</v>
+      </c>
+      <c r="G2514" s="3"/>
+      <c r="H2514" s="3"/>
+      <c r="I2514" s="3"/>
+      <c r="J2514" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2514" s="3"/>
+      <c r="L2514" s="3"/>
+      <c r="M2514" s="3"/>
+    </row>
+    <row r="2515" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2515" s="3" t="s">
+        <v>3869</v>
+      </c>
+      <c r="B2515" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2515" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2515" s="3">
+        <v>359763125</v>
+      </c>
+      <c r="E2515" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2515" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="G2515" s="3"/>
+      <c r="H2515" s="3"/>
+      <c r="I2515" s="3"/>
+      <c r="J2515" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2515" s="3"/>
+      <c r="L2515" s="3"/>
+      <c r="M2515" s="3"/>
+    </row>
+    <row r="2516" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2516" s="3" t="s">
+        <v>3870</v>
+      </c>
+      <c r="B2516" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2516" s="3">
+        <v>466</v>
+      </c>
+      <c r="D2516" s="3">
+        <v>359769184</v>
+      </c>
+      <c r="E2516" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2516" s="3" t="s">
+        <v>3871</v>
+      </c>
+      <c r="G2516" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2516" s="3"/>
+      <c r="I2516" s="3"/>
+      <c r="J2516" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2516" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2516" s="3" t="s">
+        <v>3872</v>
+      </c>
+      <c r="M2516" s="3" t="s">
+        <v>3873</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2517" s="3" t="s">
+        <v>3874</v>
+      </c>
+      <c r="B2517" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2517" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2517" s="3">
+        <v>359771919</v>
+      </c>
+      <c r="E2517" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2517" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2517" s="3"/>
+      <c r="H2517" s="3"/>
+      <c r="I2517" s="3"/>
+      <c r="J2517" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2517" s="3"/>
+      <c r="L2517" s="3"/>
+      <c r="M2517" s="3"/>
+    </row>
+    <row r="2518" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2518" s="3" t="s">
+        <v>3875</v>
+      </c>
+      <c r="B2518" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2518" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2518" s="3">
+        <v>359780653</v>
+      </c>
+      <c r="E2518" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2518" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2518" s="3"/>
+      <c r="H2518" s="3"/>
+      <c r="I2518" s="3"/>
+      <c r="J2518" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2518" s="3"/>
+      <c r="L2518" s="3"/>
+      <c r="M2518" s="3"/>
+    </row>
+    <row r="2519" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2519" s="3" t="s">
+        <v>3876</v>
+      </c>
+      <c r="B2519" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2519" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2519" s="3">
+        <v>359812181</v>
+      </c>
+      <c r="E2519" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2519" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G2519" s="3"/>
+      <c r="H2519" s="3"/>
+      <c r="I2519" s="3"/>
+      <c r="J2519" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2519" s="3"/>
+      <c r="L2519" s="3"/>
+      <c r="M2519" s="3"/>
+    </row>
+    <row r="2520" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2520" s="3" t="s">
+        <v>3877</v>
+      </c>
+      <c r="B2520" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2520" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2520" s="3">
+        <v>359849118</v>
+      </c>
+      <c r="E2520" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2520" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2520" s="3"/>
+      <c r="H2520" s="3"/>
+      <c r="I2520" s="3"/>
+      <c r="J2520" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2520" s="3"/>
+      <c r="L2520" s="3"/>
+      <c r="M2520" s="3"/>
+    </row>
+    <row r="2521" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2521" s="3" t="s">
+        <v>3878</v>
+      </c>
+      <c r="B2521" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2521" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2521" s="3">
+        <v>359868229</v>
+      </c>
+      <c r="E2521" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2521" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G2521" s="3"/>
+      <c r="H2521" s="3"/>
+      <c r="I2521" s="3"/>
+      <c r="J2521" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2521" s="3"/>
+      <c r="L2521" s="3"/>
+      <c r="M2521" s="3"/>
+    </row>
+    <row r="2522" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2522" s="3" t="s">
+        <v>3879</v>
+      </c>
+      <c r="B2522" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2522" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2522" s="3">
+        <v>359877761</v>
+      </c>
+      <c r="E2522" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2522" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2522" s="3"/>
+      <c r="H2522" s="3"/>
+      <c r="I2522" s="3"/>
+      <c r="J2522" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2522" s="3"/>
+      <c r="L2522" s="3"/>
+      <c r="M2522" s="3"/>
+    </row>
+    <row r="2523" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2523" s="3" t="s">
+        <v>3880</v>
+      </c>
+      <c r="B2523" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2523" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2523" s="3">
+        <v>359889099</v>
+      </c>
+      <c r="E2523" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2523" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G2523" s="3"/>
+      <c r="H2523" s="3"/>
+      <c r="I2523" s="3"/>
+      <c r="J2523" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2523" s="3"/>
+      <c r="L2523" s="3"/>
+      <c r="M2523" s="3"/>
+    </row>
+    <row r="2524" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2524" s="3" t="s">
+        <v>3881</v>
+      </c>
+      <c r="B2524" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2524" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2524" s="3">
+        <v>359893992</v>
+      </c>
+      <c r="E2524" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2524" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G2524" s="3"/>
+      <c r="H2524" s="3"/>
+      <c r="I2524" s="3"/>
+      <c r="J2524" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2524" s="3"/>
+      <c r="L2524" s="3"/>
+      <c r="M2524" s="3"/>
+    </row>
+    <row r="2525" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2525" s="3" t="s">
+        <v>3882</v>
+      </c>
+      <c r="B2525" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2525" s="3">
+        <v>558</v>
+      </c>
+      <c r="D2525" s="3">
+        <v>359895636</v>
+      </c>
+      <c r="E2525" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2525" s="3" t="s">
+        <v>3883</v>
+      </c>
+      <c r="G2525" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2525" s="3"/>
+      <c r="I2525" s="3"/>
+      <c r="J2525" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2525" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2525" s="3" t="s">
+        <v>3884</v>
+      </c>
+      <c r="M2525" s="3"/>
+    </row>
+    <row r="2526" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2526" s="3" t="s">
+        <v>3885</v>
+      </c>
+      <c r="B2526" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2526" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2526" s="3">
+        <v>359904302</v>
+      </c>
+      <c r="E2526" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2526" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2526" s="3"/>
+      <c r="H2526" s="3"/>
+      <c r="I2526" s="3"/>
+      <c r="J2526" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2526" s="3"/>
+      <c r="L2526" s="3"/>
+      <c r="M2526" s="3"/>
+    </row>
+    <row r="2527" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2527" s="3" t="s">
+        <v>3886</v>
+      </c>
+      <c r="B2527" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2527" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2527" s="3">
+        <v>359905632</v>
+      </c>
+      <c r="E2527" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2527" s="3" t="s">
+        <v>2484</v>
+      </c>
+      <c r="G2527" s="3"/>
+      <c r="H2527" s="3"/>
+      <c r="I2527" s="3"/>
+      <c r="J2527" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2527" s="3"/>
+      <c r="L2527" s="3"/>
+      <c r="M2527" s="3"/>
+    </row>
+    <row r="2528" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2528" s="3" t="s">
+        <v>3887</v>
+      </c>
+      <c r="B2528" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2528" s="3">
+        <v>473</v>
+      </c>
+      <c r="D2528" s="3">
+        <v>359925370</v>
+      </c>
+      <c r="E2528" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2528" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G2528" s="3"/>
+      <c r="H2528" s="3">
+        <v>25</v>
+      </c>
+      <c r="I2528" s="3"/>
+      <c r="J2528" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2528" s="3"/>
+      <c r="L2528" s="3"/>
+      <c r="M2528" s="3"/>
+    </row>
+    <row r="2529" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2529" s="3" t="s">
+        <v>3888</v>
+      </c>
+      <c r="B2529" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2529" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2529" s="3">
+        <v>359929523</v>
+      </c>
+      <c r="E2529" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2529" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G2529" s="3"/>
+      <c r="H2529" s="3"/>
+      <c r="I2529" s="3"/>
+      <c r="J2529" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2529" s="3"/>
+      <c r="L2529" s="3"/>
+      <c r="M2529" s="3"/>
+    </row>
+    <row r="2530" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2530" s="3" t="s">
+        <v>3889</v>
+      </c>
+      <c r="B2530" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2530" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2530" s="3">
+        <v>359963515</v>
+      </c>
+      <c r="E2530" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2530" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2530" s="3"/>
+      <c r="H2530" s="3"/>
+      <c r="I2530" s="3"/>
+      <c r="J2530" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2530" s="3"/>
+      <c r="L2530" s="3"/>
+      <c r="M2530" s="3"/>
+    </row>
+    <row r="2531" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2531" s="3" t="s">
+        <v>3890</v>
+      </c>
+      <c r="B2531" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2531" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2531" s="3">
+        <v>359990695</v>
+      </c>
+      <c r="E2531" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2531" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2531" s="3"/>
+      <c r="H2531" s="3"/>
+      <c r="I2531" s="3"/>
+      <c r="J2531" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2531" s="3"/>
+      <c r="L2531" s="3"/>
+      <c r="M2531" s="3"/>
+    </row>
+    <row r="2532" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2532" s="3" t="s">
+        <v>3891</v>
+      </c>
+      <c r="B2532" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2532" s="3">
+        <v>461</v>
+      </c>
+      <c r="D2532" s="3">
+        <v>359995690</v>
+      </c>
+      <c r="E2532" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2532" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2532" s="3"/>
+      <c r="H2532" s="3"/>
+      <c r="I2532" s="3"/>
+      <c r="J2532" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2532" s="3"/>
+      <c r="L2532" s="3"/>
+      <c r="M2532" s="3"/>
+    </row>
+    <row r="2533" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2533" s="3" t="s">
+        <v>3892</v>
+      </c>
+      <c r="B2533" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2533" s="3">
+        <v>558</v>
+      </c>
+      <c r="D2533" s="3">
+        <v>360060986</v>
+      </c>
+      <c r="E2533" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2533" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G2533" s="3"/>
+      <c r="H2533" s="3"/>
+      <c r="I2533" s="3"/>
+      <c r="J2533" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2533" s="3"/>
+      <c r="L2533" s="3"/>
+      <c r="M2533" s="3"/>
+    </row>
+    <row r="2534" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2534" s="3" t="s">
+        <v>3893</v>
+      </c>
+      <c r="B2534" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2534" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2534" s="3">
+        <v>360086785</v>
+      </c>
+      <c r="E2534" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2534" s="3" t="s">
+        <v>3894</v>
+      </c>
+      <c r="G2534" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2534" s="3"/>
+      <c r="I2534" s="3"/>
+      <c r="J2534" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2534" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2534" s="3" t="s">
+        <v>3895</v>
+      </c>
+      <c r="M2534" s="3"/>
+    </row>
+    <row r="2535" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2535" s="3" t="s">
+        <v>3896</v>
+      </c>
+      <c r="B2535" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2535" s="3">
+        <v>463</v>
+      </c>
+      <c r="D2535" s="3">
+        <v>360105069</v>
+      </c>
+      <c r="E2535" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2535" s="3" t="s">
+        <v>3897</v>
+      </c>
+      <c r="G2535" s="3"/>
+      <c r="H2535" s="3"/>
+      <c r="I2535" s="3"/>
+      <c r="J2535" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2535" s="3"/>
+      <c r="L2535" s="3"/>
+      <c r="M2535" s="3"/>
+    </row>
+    <row r="2536" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2536" s="3" t="s">
+        <v>3898</v>
+      </c>
+      <c r="B2536" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2536" s="3">
+        <v>473</v>
+      </c>
+      <c r="D2536" s="3">
+        <v>360106434</v>
+      </c>
+      <c r="E2536" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2536" s="3" t="s">
+        <v>3158</v>
+      </c>
+      <c r="G2536" s="3"/>
+      <c r="H2536" s="3"/>
+      <c r="I2536" s="3"/>
+      <c r="J2536" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2536" s="3"/>
+      <c r="L2536" s="3"/>
+      <c r="M2536" s="3"/>
+    </row>
+    <row r="2537" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2537" s="3" t="s">
+        <v>3899</v>
+      </c>
+      <c r="B2537" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2537" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2537" s="3">
+        <v>360144242</v>
+      </c>
+      <c r="E2537" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2537" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="G2537" s="3"/>
+      <c r="H2537" s="3"/>
+      <c r="I2537" s="3"/>
+      <c r="J2537" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2537" s="3"/>
+      <c r="L2537" s="3"/>
+      <c r="M2537" s="3"/>
+    </row>
+    <row r="2538" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2538" s="3" t="s">
+        <v>3900</v>
+      </c>
+      <c r="B2538" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2538" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2538" s="3">
+        <v>360155233</v>
+      </c>
+      <c r="E2538" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2538" s="3" t="s">
+        <v>3901</v>
+      </c>
+      <c r="G2538" s="3"/>
+      <c r="H2538" s="3"/>
+      <c r="I2538" s="3"/>
+      <c r="J2538" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2538" s="3"/>
+      <c r="L2538" s="3"/>
+      <c r="M2538" s="3"/>
+    </row>
+    <row r="2539" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2539" s="3" t="s">
+        <v>3902</v>
+      </c>
+      <c r="B2539" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C2539" s="3">
+        <v>477</v>
+      </c>
+      <c r="D2539" s="3">
+        <v>360159728</v>
+      </c>
+      <c r="E2539" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2539" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2539" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2539" s="3"/>
+      <c r="I2539" s="3"/>
+      <c r="J2539" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2539" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2539" s="3" t="s">
+        <v>3903</v>
+      </c>
+      <c r="M2539" s="3" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2540" s="3" t="s">
+        <v>3905</v>
+      </c>
+      <c r="B2540" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2540" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2540" s="3">
+        <v>360167665</v>
+      </c>
+      <c r="E2540" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2540" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2540" s="3"/>
+      <c r="H2540" s="3"/>
+      <c r="I2540" s="3"/>
+      <c r="J2540" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2540" s="3"/>
+      <c r="L2540" s="3"/>
+      <c r="M2540" s="3"/>
+    </row>
+    <row r="2541" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2541" s="3" t="s">
+        <v>3906</v>
+      </c>
+      <c r="B2541" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2541" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2541" s="3">
+        <v>360177621</v>
+      </c>
+      <c r="E2541" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2541" s="3" t="s">
+        <v>2976</v>
+      </c>
+      <c r="G2541" s="3"/>
+      <c r="H2541" s="3"/>
+      <c r="I2541" s="3"/>
+      <c r="J2541" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2541" s="3"/>
+      <c r="L2541" s="3"/>
+      <c r="M2541" s="3"/>
+    </row>
+    <row r="2542" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2542" s="3" t="s">
+        <v>3907</v>
+      </c>
+      <c r="B2542" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2542" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2542" s="3">
+        <v>360181819</v>
+      </c>
+      <c r="E2542" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2542" s="3" t="s">
+        <v>3908</v>
+      </c>
+      <c r="G2542" s="3"/>
+      <c r="H2542" s="3"/>
+      <c r="I2542" s="3"/>
+      <c r="J2542" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2542" s="3"/>
+      <c r="L2542" s="3"/>
+      <c r="M2542" s="3"/>
+    </row>
+    <row r="2543" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2543" s="3" t="s">
+        <v>3909</v>
+      </c>
+      <c r="B2543" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2543" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2543" s="3">
+        <v>360182489</v>
+      </c>
+      <c r="E2543" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2543" s="3" t="s">
+        <v>3910</v>
+      </c>
+      <c r="G2543" s="3"/>
+      <c r="H2543" s="3"/>
+      <c r="I2543" s="3"/>
+      <c r="J2543" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2543" s="3"/>
+      <c r="L2543" s="3"/>
+      <c r="M2543" s="3"/>
+    </row>
+    <row r="2544" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2544" s="3" t="s">
+        <v>3911</v>
+      </c>
+      <c r="B2544" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2544" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2544" s="3">
+        <v>360182811</v>
+      </c>
+      <c r="E2544" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2544" s="3" t="s">
+        <v>3912</v>
+      </c>
+      <c r="G2544" s="3"/>
+      <c r="H2544" s="3"/>
+      <c r="I2544" s="3"/>
+      <c r="J2544" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2544" s="3"/>
+      <c r="L2544" s="3"/>
+      <c r="M2544" s="3"/>
+    </row>
+    <row r="2545" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2545" s="3" t="s">
+        <v>3913</v>
+      </c>
+      <c r="B2545" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2545" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2545" s="3">
+        <v>360202436</v>
+      </c>
+      <c r="E2545" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2545" s="3" t="s">
+        <v>2401</v>
+      </c>
+      <c r="G2545" s="3"/>
+      <c r="H2545" s="3"/>
+      <c r="I2545" s="3"/>
+      <c r="J2545" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2545" s="3"/>
+      <c r="L2545" s="3"/>
+      <c r="M2545" s="3"/>
+    </row>
+    <row r="2546" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2546" s="3" t="s">
+        <v>3914</v>
+      </c>
+      <c r="B2546" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2546" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2546" s="3">
+        <v>360203571</v>
+      </c>
+      <c r="E2546" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2546" s="3" t="s">
+        <v>2401</v>
+      </c>
+      <c r="G2546" s="3"/>
+      <c r="H2546" s="3"/>
+      <c r="I2546" s="3"/>
+      <c r="J2546" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2546" s="3"/>
+      <c r="L2546" s="3"/>
+      <c r="M2546" s="3"/>
+    </row>
+    <row r="2547" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2547" s="3" t="s">
+        <v>3915</v>
+      </c>
+      <c r="B2547" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2547" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2547" s="3">
+        <v>360204727</v>
+      </c>
+      <c r="E2547" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2547" s="3" t="s">
+        <v>3916</v>
+      </c>
+      <c r="G2547" s="3"/>
+      <c r="H2547" s="3"/>
+      <c r="I2547" s="3"/>
+      <c r="J2547" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2547" s="3"/>
+      <c r="L2547" s="3"/>
+      <c r="M2547" s="3"/>
+    </row>
+    <row r="2548" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2548" s="3" t="s">
+        <v>3917</v>
+      </c>
+      <c r="B2548" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2548" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2548" s="3">
+        <v>360205039</v>
+      </c>
+      <c r="E2548" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2548" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G2548" s="3"/>
+      <c r="H2548" s="3"/>
+      <c r="I2548" s="3"/>
+      <c r="J2548" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2548" s="3"/>
+      <c r="L2548" s="3"/>
+      <c r="M2548" s="3"/>
+    </row>
+    <row r="2549" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2549" s="3" t="s">
+        <v>3918</v>
+      </c>
+      <c r="B2549" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2549" s="3">
+        <v>558</v>
+      </c>
+      <c r="D2549" s="3">
+        <v>360215133</v>
+      </c>
+      <c r="E2549" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2549" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G2549" s="3"/>
+      <c r="H2549" s="3"/>
+      <c r="I2549" s="3"/>
+      <c r="J2549" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2549" s="3"/>
+      <c r="L2549" s="3"/>
+      <c r="M2549" s="3"/>
+    </row>
+    <row r="2550" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2550" s="3" t="s">
+        <v>3919</v>
+      </c>
+      <c r="B2550" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2550" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2550" s="3">
+        <v>360219480</v>
+      </c>
+      <c r="E2550" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2550" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="G2550" s="3"/>
+      <c r="H2550" s="3"/>
+      <c r="I2550" s="3"/>
+      <c r="J2550" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2550" s="3"/>
+      <c r="L2550" s="3"/>
+      <c r="M2550" s="3"/>
+    </row>
+    <row r="2551" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2551" s="3" t="s">
+        <v>3920</v>
+      </c>
+      <c r="B2551" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2551" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2551" s="3">
+        <v>360225375</v>
+      </c>
+      <c r="E2551" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2551" s="3" t="s">
+        <v>3921</v>
+      </c>
+      <c r="G2551" s="3"/>
+      <c r="H2551" s="3"/>
+      <c r="I2551" s="3"/>
+      <c r="J2551" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2551" s="3"/>
+      <c r="L2551" s="3"/>
+      <c r="M2551" s="3"/>
+    </row>
+    <row r="2552" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2552" s="3" t="s">
+        <v>3922</v>
+      </c>
+      <c r="B2552" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2552" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2552" s="3">
+        <v>360228958</v>
+      </c>
+      <c r="E2552" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2552" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G2552" s="3"/>
+      <c r="H2552" s="3"/>
+      <c r="I2552" s="3"/>
+      <c r="J2552" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2552" s="3"/>
+      <c r="L2552" s="3"/>
+      <c r="M2552" s="3"/>
+    </row>
+    <row r="2553" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2553" s="3" t="s">
+        <v>3923</v>
+      </c>
+      <c r="B2553" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2553" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2553" s="3">
+        <v>360233563</v>
+      </c>
+      <c r="E2553" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2553" s="3" t="s">
+        <v>3924</v>
+      </c>
+      <c r="G2553" s="3"/>
+      <c r="H2553" s="3"/>
+      <c r="I2553" s="3"/>
+      <c r="J2553" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2553" s="3"/>
+      <c r="L2553" s="3"/>
+      <c r="M2553" s="3"/>
+    </row>
+    <row r="2554" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2554" s="3" t="s">
+        <v>3925</v>
+      </c>
+      <c r="B2554" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2554" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2554" s="3">
+        <v>360254282</v>
+      </c>
+      <c r="E2554" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2554" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G2554" s="3"/>
+      <c r="H2554" s="3"/>
+      <c r="I2554" s="3"/>
+      <c r="J2554" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2554" s="3"/>
+      <c r="L2554" s="3"/>
+      <c r="M2554" s="3"/>
+    </row>
+    <row r="2555" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2555" s="3" t="s">
+        <v>3926</v>
+      </c>
+      <c r="B2555" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2555" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2555" s="3">
+        <v>360290790</v>
+      </c>
+      <c r="E2555" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2555" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2555" s="3"/>
+      <c r="H2555" s="3"/>
+      <c r="I2555" s="3"/>
+      <c r="J2555" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2555" s="3"/>
+      <c r="L2555" s="3"/>
+      <c r="M2555" s="3"/>
+    </row>
+    <row r="2556" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2556" s="3" t="s">
+        <v>3927</v>
+      </c>
+      <c r="B2556" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2556" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2556" s="3">
+        <v>360294675</v>
+      </c>
+      <c r="E2556" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2556" s="3" t="s">
+        <v>3928</v>
+      </c>
+      <c r="G2556" s="3"/>
+      <c r="H2556" s="3"/>
+      <c r="I2556" s="3"/>
+      <c r="J2556" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2556" s="3"/>
+      <c r="L2556" s="3"/>
+      <c r="M2556" s="3"/>
+    </row>
+    <row r="2557" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2557" s="3" t="s">
+        <v>3929</v>
+      </c>
+      <c r="B2557" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2557" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2557" s="3">
+        <v>360310033</v>
+      </c>
+      <c r="E2557" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2557" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G2557" s="3"/>
+      <c r="H2557" s="3"/>
+      <c r="I2557" s="3"/>
+      <c r="J2557" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2557" s="3"/>
+      <c r="L2557" s="3"/>
+      <c r="M2557" s="3"/>
+    </row>
+    <row r="2558" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2558" s="3" t="s">
+        <v>3930</v>
+      </c>
+      <c r="B2558" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2558" s="3">
+        <v>463</v>
+      </c>
+      <c r="D2558" s="3">
+        <v>360314847</v>
+      </c>
+      <c r="E2558" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2558" s="3" t="s">
+        <v>3931</v>
+      </c>
+      <c r="G2558" s="3"/>
+      <c r="H2558" s="3"/>
+      <c r="I2558" s="3"/>
+      <c r="J2558" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2558" s="3"/>
+      <c r="L2558" s="3"/>
+      <c r="M2558" s="3"/>
+    </row>
+    <row r="2559" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2559" s="3" t="s">
+        <v>3932</v>
+      </c>
+      <c r="B2559" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2559" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2559" s="3">
+        <v>360314380</v>
+      </c>
+      <c r="E2559" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2559" s="3" t="s">
+        <v>2367</v>
+      </c>
+      <c r="G2559" s="3"/>
+      <c r="H2559" s="3"/>
+      <c r="I2559" s="3"/>
+      <c r="J2559" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2559" s="3"/>
+      <c r="L2559" s="3"/>
+      <c r="M2559" s="3"/>
+    </row>
+    <row r="2560" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2560" s="3" t="s">
+        <v>3933</v>
+      </c>
+      <c r="B2560" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2560" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2560" s="3">
+        <v>360314788</v>
+      </c>
+      <c r="E2560" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2560" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2560" s="3"/>
+      <c r="H2560" s="3"/>
+      <c r="I2560" s="3"/>
+      <c r="J2560" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2560" s="3"/>
+      <c r="L2560" s="3"/>
+      <c r="M2560" s="3"/>
+    </row>
+    <row r="2561" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2561" s="3" t="s">
+        <v>3934</v>
+      </c>
+      <c r="B2561" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2561" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2561" s="3">
+        <v>360331006</v>
+      </c>
+      <c r="E2561" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2561" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2561" s="3"/>
+      <c r="H2561" s="3"/>
+      <c r="I2561" s="3"/>
+      <c r="J2561" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2561" s="3"/>
+      <c r="L2561" s="3"/>
+      <c r="M2561" s="3"/>
+    </row>
+    <row r="2562" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2562" s="3" t="s">
+        <v>3935</v>
+      </c>
+      <c r="B2562" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2562" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2562" s="3">
+        <v>360332627</v>
+      </c>
+      <c r="E2562" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2562" s="3" t="s">
+        <v>3936</v>
+      </c>
+      <c r="G2562" s="3"/>
+      <c r="H2562" s="3"/>
+      <c r="I2562" s="3"/>
+      <c r="J2562" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2562" s="3"/>
+      <c r="L2562" s="3"/>
+      <c r="M2562" s="3"/>
+    </row>
+    <row r="2563" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2563" s="3" t="s">
+        <v>3937</v>
+      </c>
+      <c r="B2563" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2563" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2563" s="3">
+        <v>360332818</v>
+      </c>
+      <c r="E2563" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2563" s="3" t="s">
+        <v>2454</v>
+      </c>
+      <c r="G2563" s="3"/>
+      <c r="H2563" s="3">
+        <v>3</v>
+      </c>
+      <c r="I2563" s="3"/>
+      <c r="J2563" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2563" s="3"/>
+      <c r="L2563" s="3"/>
+      <c r="M2563" s="3"/>
+    </row>
+    <row r="2564" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2564" s="3" t="s">
+        <v>3938</v>
+      </c>
+      <c r="B2564" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2564" s="3">
+        <v>536</v>
+      </c>
+      <c r="D2564" s="3">
+        <v>360339703</v>
+      </c>
+      <c r="E2564" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2564" s="3" t="s">
+        <v>3939</v>
+      </c>
+      <c r="G2564" s="3"/>
+      <c r="H2564" s="3"/>
+      <c r="I2564" s="3"/>
+      <c r="J2564" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2564" s="3"/>
+      <c r="L2564" s="3"/>
+      <c r="M2564" s="3"/>
+    </row>
+    <row r="2565" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2565" s="3" t="s">
+        <v>3940</v>
+      </c>
+      <c r="B2565" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2565" s="3">
+        <v>536</v>
+      </c>
+      <c r="D2565" s="3">
+        <v>360349125</v>
+      </c>
+      <c r="E2565" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2565" s="3" t="s">
+        <v>2434</v>
+      </c>
+      <c r="G2565" s="3"/>
+      <c r="H2565" s="3"/>
+      <c r="I2565" s="3"/>
+      <c r="J2565" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2565" s="3"/>
+      <c r="L2565" s="3"/>
+      <c r="M2565" s="3"/>
+    </row>
+    <row r="2566" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2566" s="3" t="s">
+        <v>3941</v>
+      </c>
+      <c r="B2566" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2566" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2566" s="3">
+        <v>360359832</v>
+      </c>
+      <c r="E2566" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2566" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2566" s="3"/>
+      <c r="H2566" s="3"/>
+      <c r="I2566" s="3"/>
+      <c r="J2566" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2566" s="3"/>
+      <c r="L2566" s="3"/>
+      <c r="M2566" s="3"/>
+    </row>
+    <row r="2567" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2567" s="3" t="s">
+        <v>3942</v>
+      </c>
+      <c r="B2567" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2567" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2567" s="3">
+        <v>360390157</v>
+      </c>
+      <c r="E2567" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2567" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2567" s="3"/>
+      <c r="H2567" s="3"/>
+      <c r="I2567" s="3"/>
+      <c r="J2567" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2567" s="3"/>
+      <c r="L2567" s="3"/>
+      <c r="M2567" s="3"/>
+    </row>
+    <row r="2568" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2568" s="3" t="s">
+        <v>3943</v>
+      </c>
+      <c r="B2568" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2568" s="3">
+        <v>461</v>
+      </c>
+      <c r="D2568" s="3">
+        <v>360417440</v>
+      </c>
+      <c r="E2568" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2568" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2568" s="3"/>
+      <c r="H2568" s="3"/>
+      <c r="I2568" s="3"/>
+      <c r="J2568" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2568" s="3"/>
+      <c r="L2568" s="3"/>
+      <c r="M2568" s="3"/>
+    </row>
+    <row r="2569" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2569" s="3" t="s">
+        <v>3944</v>
+      </c>
+      <c r="B2569" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2569" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2569" s="3">
+        <v>360418196</v>
+      </c>
+      <c r="E2569" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2569" s="3" t="s">
+        <v>3945</v>
+      </c>
+      <c r="G2569" s="3"/>
+      <c r="H2569" s="3"/>
+      <c r="I2569" s="3"/>
+      <c r="J2569" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2569" s="3"/>
+      <c r="L2569" s="3"/>
+      <c r="M2569" s="3"/>
+    </row>
+    <row r="2570" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2570" s="3" t="s">
+        <v>3946</v>
+      </c>
+      <c r="B2570" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2570" s="3">
+        <v>544</v>
+      </c>
+      <c r="D2570" s="3">
+        <v>360435901</v>
+      </c>
+      <c r="E2570" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2570" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G2570" s="3"/>
+      <c r="H2570" s="3"/>
+      <c r="I2570" s="3"/>
+      <c r="J2570" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2570" s="3"/>
+      <c r="L2570" s="3"/>
+      <c r="M2570" s="3"/>
+    </row>
+    <row r="2571" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2571" s="3" t="s">
+        <v>3947</v>
+      </c>
+      <c r="B2571" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2571" s="3">
+        <v>551</v>
+      </c>
+      <c r="D2571" s="3">
+        <v>360437007</v>
+      </c>
+      <c r="E2571" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2571" s="3" t="s">
+        <v>2714</v>
+      </c>
+      <c r="G2571" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2571" s="3"/>
+      <c r="I2571" s="3"/>
+      <c r="J2571" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2571" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2571" s="3" t="s">
+        <v>3948</v>
+      </c>
+      <c r="M2571" s="3"/>
+    </row>
+    <row r="2572" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2572" s="3" t="s">
+        <v>3949</v>
+      </c>
+      <c r="B2572" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2572" s="3">
+        <v>558</v>
+      </c>
+      <c r="D2572" s="3">
+        <v>360470302</v>
+      </c>
+      <c r="E2572" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2572" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G2572" s="3"/>
+      <c r="H2572" s="3"/>
+      <c r="I2572" s="3"/>
+      <c r="J2572" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2572" s="3"/>
+      <c r="L2572" s="3"/>
+      <c r="M2572" s="3"/>
+    </row>
+    <row r="2573" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2573" s="3" t="s">
+        <v>3950</v>
+      </c>
+      <c r="B2573" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2573" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2573" s="3">
+        <v>360478997</v>
+      </c>
+      <c r="E2573" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2573" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G2573" s="3"/>
+      <c r="H2573" s="3"/>
+      <c r="I2573" s="3"/>
+      <c r="J2573" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2573" s="3"/>
+      <c r="L2573" s="3"/>
+      <c r="M2573" s="3"/>
+    </row>
+    <row r="2574" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2574" s="3" t="s">
+        <v>3951</v>
+      </c>
+      <c r="B2574" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C2574" s="3">
+        <v>550</v>
+      </c>
+      <c r="D2574" s="3">
+        <v>360483826</v>
+      </c>
+      <c r="E2574" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2574" s="3" t="s">
+        <v>2140</v>
+      </c>
+      <c r="G2574" s="3"/>
+      <c r="H2574" s="3"/>
+      <c r="I2574" s="3"/>
+      <c r="J2574" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2574" s="3"/>
+      <c r="L2574" s="3"/>
+      <c r="M2574" s="3"/>
+    </row>
+    <row r="2575" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2575" s="3" t="s">
+        <v>3952</v>
+      </c>
+      <c r="B2575" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2575" s="3">
+        <v>473</v>
+      </c>
+      <c r="D2575" s="3">
+        <v>360541001</v>
+      </c>
+      <c r="E2575" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2575" s="3" t="s">
+        <v>2335</v>
+      </c>
+      <c r="G2575" s="3"/>
+      <c r="H2575" s="3"/>
+      <c r="I2575" s="3"/>
+      <c r="J2575" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2575" s="3"/>
+      <c r="L2575" s="3"/>
+      <c r="M2575" s="3"/>
+    </row>
+    <row r="2576" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2576" s="3" t="s">
+        <v>3953</v>
+      </c>
+      <c r="B2576" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2576" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2576" s="3">
+        <v>360575331</v>
+      </c>
+      <c r="E2576" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2576" s="3" t="s">
+        <v>3954</v>
+      </c>
+      <c r="G2576" s="3"/>
+      <c r="H2576" s="3"/>
+      <c r="I2576" s="3"/>
+      <c r="J2576" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2576" s="3"/>
+      <c r="L2576" s="3"/>
+      <c r="M2576" s="3"/>
+    </row>
+    <row r="2577" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2577" s="3" t="s">
+        <v>3955</v>
+      </c>
+      <c r="B2577" s="3" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C2577" s="3">
+        <v>537</v>
+      </c>
+      <c r="D2577" s="3">
+        <v>360595159</v>
+      </c>
+      <c r="E2577" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2577" s="3" t="s">
+        <v>3956</v>
+      </c>
+      <c r="G2577" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2577" s="3"/>
+      <c r="I2577" s="3"/>
+      <c r="J2577" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2577" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2577" s="3" t="s">
+        <v>3957</v>
+      </c>
+      <c r="M2577" s="3"/>
+    </row>
+    <row r="2578" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2578" s="3" t="s">
+        <v>3958</v>
+      </c>
+      <c r="B2578" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2578" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2578" s="3">
+        <v>360627372</v>
+      </c>
+      <c r="E2578" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2578" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G2578" s="3"/>
+      <c r="H2578" s="3"/>
+      <c r="I2578" s="3"/>
+      <c r="J2578" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2578" s="3"/>
+      <c r="L2578" s="3"/>
+      <c r="M2578" s="3"/>
+    </row>
+    <row r="2579" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2579" s="3" t="s">
+        <v>3959</v>
+      </c>
+      <c r="B2579" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2579" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2579" s="3">
+        <v>360647064</v>
+      </c>
+      <c r="E2579" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2579" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2579" s="3"/>
+      <c r="H2579" s="3">
+        <v>29</v>
+      </c>
+      <c r="I2579" s="3"/>
+      <c r="J2579" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2579" s="3"/>
+      <c r="L2579" s="3"/>
+      <c r="M2579" s="3"/>
+    </row>
+    <row r="2580" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2580" s="3" t="s">
+        <v>3960</v>
+      </c>
+      <c r="B2580" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2580" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2580" s="3">
+        <v>360692347</v>
+      </c>
+      <c r="E2580" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2580" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2580" s="3"/>
+      <c r="H2580" s="3"/>
+      <c r="I2580" s="3"/>
+      <c r="J2580" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2580" s="3"/>
+      <c r="L2580" s="3"/>
+      <c r="M2580" s="3"/>
+    </row>
+    <row r="2581" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2581" s="3" t="s">
+        <v>3961</v>
+      </c>
+      <c r="B2581" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2581" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2581" s="3">
+        <v>360692252</v>
+      </c>
+      <c r="E2581" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2581" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G2581" s="3"/>
+      <c r="H2581" s="3"/>
+      <c r="I2581" s="3"/>
+      <c r="J2581" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2581" s="3"/>
+      <c r="L2581" s="3"/>
+      <c r="M2581" s="3"/>
+    </row>
+    <row r="2582" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2582" s="3" t="s">
+        <v>3962</v>
+      </c>
+      <c r="B2582" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2582" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2582" s="3">
+        <v>360740594</v>
+      </c>
+      <c r="E2582" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2582" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G2582" s="3"/>
+      <c r="H2582" s="3"/>
+      <c r="I2582" s="3"/>
+      <c r="J2582" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2582" s="3"/>
+      <c r="L2582" s="3"/>
+      <c r="M2582" s="3"/>
+    </row>
+    <row r="2583" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2583" s="3" t="s">
+        <v>3963</v>
+      </c>
+      <c r="B2583" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2583" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2583" s="3">
+        <v>360742919</v>
+      </c>
+      <c r="E2583" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2583" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2583" s="3"/>
+      <c r="H2583" s="3"/>
+      <c r="I2583" s="3"/>
+      <c r="J2583" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2583" s="3"/>
+      <c r="L2583" s="3"/>
+      <c r="M2583" s="3"/>
+    </row>
+    <row r="2584" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2584" s="3" t="s">
+        <v>3964</v>
+      </c>
+      <c r="B2584" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2584" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2584" s="3">
+        <v>360766133</v>
+      </c>
+      <c r="E2584" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2584" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2584" s="3"/>
+      <c r="H2584" s="3"/>
+      <c r="I2584" s="3"/>
+      <c r="J2584" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2584" s="3"/>
+      <c r="L2584" s="3"/>
+      <c r="M2584" s="3"/>
+    </row>
+    <row r="2585" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2585" s="3" t="s">
+        <v>3965</v>
+      </c>
+      <c r="B2585" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2585" s="3">
+        <v>473</v>
+      </c>
+      <c r="D2585" s="3">
+        <v>360770334</v>
+      </c>
+      <c r="E2585" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2585" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2585" s="3"/>
+      <c r="H2585" s="3"/>
+      <c r="I2585" s="3"/>
+      <c r="J2585" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2585" s="3"/>
+      <c r="L2585" s="3"/>
+      <c r="M2585" s="3"/>
+    </row>
+    <row r="2586" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2586" s="3" t="s">
+        <v>3966</v>
+      </c>
+      <c r="B2586" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2586" s="3">
+        <v>558</v>
+      </c>
+      <c r="D2586" s="3">
+        <v>360779611</v>
+      </c>
+      <c r="E2586" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2586" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G2586" s="3"/>
+      <c r="H2586" s="3"/>
+      <c r="I2586" s="3"/>
+      <c r="J2586" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2586" s="3"/>
+      <c r="L2586" s="3"/>
+      <c r="M2586" s="3"/>
+    </row>
+    <row r="2587" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2587" s="3" t="s">
+        <v>3967</v>
+      </c>
+      <c r="B2587" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2587" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2587" s="3">
+        <v>360786233</v>
+      </c>
+      <c r="E2587" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2587" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2587" s="3"/>
+      <c r="H2587" s="3"/>
+      <c r="I2587" s="3"/>
+      <c r="J2587" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2587" s="3"/>
+      <c r="L2587" s="3"/>
+      <c r="M2587" s="3"/>
+    </row>
+    <row r="2588" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2588" s="3" t="s">
+        <v>3968</v>
+      </c>
+      <c r="B2588" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2588" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2588" s="3">
+        <v>360798876</v>
+      </c>
+      <c r="E2588" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2588" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2588" s="3"/>
+      <c r="H2588" s="3"/>
+      <c r="I2588" s="3"/>
+      <c r="J2588" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2588" s="3"/>
+      <c r="L2588" s="3"/>
+      <c r="M2588" s="3"/>
+    </row>
+    <row r="2589" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2589" s="3" t="s">
+        <v>3969</v>
+      </c>
+      <c r="B2589" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C2589" s="3">
+        <v>555</v>
+      </c>
+      <c r="D2589" s="3">
+        <v>360823664</v>
+      </c>
+      <c r="E2589" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2589" s="3" t="s">
+        <v>3970</v>
+      </c>
+      <c r="G2589" s="3"/>
+      <c r="H2589" s="3"/>
+      <c r="I2589" s="3"/>
+      <c r="J2589" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2589" s="3"/>
+      <c r="L2589" s="3"/>
+      <c r="M2589" s="3"/>
+    </row>
+    <row r="2590" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2590" s="3" t="s">
+        <v>3971</v>
+      </c>
+      <c r="B2590" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2590" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2590" s="3">
+        <v>360823619</v>
+      </c>
+      <c r="E2590" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2590" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2590" s="3"/>
+      <c r="H2590" s="3"/>
+      <c r="I2590" s="3"/>
+      <c r="J2590" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2590" s="3"/>
+      <c r="L2590" s="3"/>
+      <c r="M2590" s="3"/>
+    </row>
+    <row r="2591" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2591" s="3" t="s">
+        <v>3972</v>
+      </c>
+      <c r="B2591" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2591" s="3">
+        <v>536</v>
+      </c>
+      <c r="D2591" s="3">
+        <v>360828228</v>
+      </c>
+      <c r="E2591" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2591" s="3" t="s">
+        <v>2434</v>
+      </c>
+      <c r="G2591" s="3"/>
+      <c r="H2591" s="3"/>
+      <c r="I2591" s="3"/>
+      <c r="J2591" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2591" s="3"/>
+      <c r="L2591" s="3"/>
+      <c r="M2591" s="3"/>
+    </row>
+    <row r="2592" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2592" s="3" t="s">
+        <v>3973</v>
+      </c>
+      <c r="B2592" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2592" s="3">
+        <v>461</v>
+      </c>
+      <c r="D2592" s="3">
+        <v>360832435</v>
+      </c>
+      <c r="E2592" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2592" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2592" s="3"/>
+      <c r="H2592" s="3"/>
+      <c r="I2592" s="3"/>
+      <c r="J2592" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2592" s="3"/>
+      <c r="L2592" s="3"/>
+      <c r="M2592" s="3"/>
+    </row>
+    <row r="2593" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2593" s="3" t="s">
+        <v>3974</v>
+      </c>
+      <c r="B2593" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C2593" s="3">
+        <v>541</v>
+      </c>
+      <c r="D2593" s="3">
+        <v>360855037</v>
+      </c>
+      <c r="E2593" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2593" s="3" t="s">
+        <v>2451</v>
+      </c>
+      <c r="G2593" s="3"/>
+      <c r="H2593" s="3"/>
+      <c r="I2593" s="3"/>
+      <c r="J2593" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2593" s="3"/>
+      <c r="L2593" s="3"/>
+      <c r="M2593" s="3"/>
+    </row>
+    <row r="2594" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2594" s="3" t="s">
+        <v>3975</v>
+      </c>
+      <c r="B2594" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2594" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2594" s="3">
+        <v>360881557</v>
+      </c>
+      <c r="E2594" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2594" s="3" t="s">
+        <v>3473</v>
+      </c>
+      <c r="G2594" s="3"/>
+      <c r="H2594" s="3"/>
+      <c r="I2594" s="3"/>
+      <c r="J2594" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2594" s="3"/>
+      <c r="L2594" s="3"/>
+      <c r="M2594" s="3"/>
+    </row>
+    <row r="2595" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2595" s="3" t="s">
+        <v>3976</v>
+      </c>
+      <c r="B2595" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2595" s="3">
+        <v>553</v>
+      </c>
+      <c r="D2595" s="3">
+        <v>360888609</v>
+      </c>
+      <c r="E2595" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2595" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2595" s="3"/>
+      <c r="H2595" s="3"/>
+      <c r="I2595" s="3"/>
+      <c r="J2595" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2595" s="3"/>
+      <c r="L2595" s="3"/>
+      <c r="M2595" s="3"/>
+    </row>
+    <row r="2596" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2596" s="3" t="s">
+        <v>3977</v>
+      </c>
+      <c r="B2596" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2596" s="3">
+        <v>558</v>
+      </c>
+      <c r="D2596" s="3">
+        <v>360892750</v>
+      </c>
+      <c r="E2596" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2596" s="3" t="s">
+        <v>3978</v>
+      </c>
+      <c r="G2596" s="3"/>
+      <c r="H2596" s="3"/>
+      <c r="I2596" s="3"/>
+      <c r="J2596" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2596" s="3"/>
+      <c r="L2596" s="3"/>
+      <c r="M2596" s="3"/>
+    </row>
+    <row r="2597" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2597" s="3" t="s">
+        <v>3979</v>
+      </c>
+      <c r="B2597" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2597" s="3">
+        <v>463</v>
+      </c>
+      <c r="D2597" s="3">
+        <v>360925864</v>
+      </c>
+      <c r="E2597" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2597" s="3" t="s">
+        <v>2089</v>
+      </c>
+      <c r="G2597" s="3"/>
+      <c r="H2597" s="3"/>
+      <c r="I2597" s="3"/>
+      <c r="J2597" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2597" s="3"/>
+      <c r="L2597" s="3"/>
+      <c r="M2597" s="3"/>
+    </row>
+    <row r="2598" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2598" s="3" t="s">
+        <v>3980</v>
+      </c>
+      <c r="B2598" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2598" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2598" s="3">
+        <v>360927203</v>
+      </c>
+      <c r="E2598" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2598" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="G2598" s="3"/>
+      <c r="H2598" s="3"/>
+      <c r="I2598" s="3"/>
+      <c r="J2598" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2598" s="3"/>
+      <c r="L2598" s="3"/>
+      <c r="M2598" s="3"/>
+    </row>
+    <row r="2599" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2599" s="3" t="s">
+        <v>3981</v>
+      </c>
+      <c r="B2599" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2599" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2599" s="3">
+        <v>360929882</v>
+      </c>
+      <c r="E2599" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2599" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G2599" s="3"/>
+      <c r="H2599" s="3"/>
+      <c r="I2599" s="3"/>
+      <c r="J2599" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2599" s="3"/>
+      <c r="L2599" s="3"/>
+      <c r="M2599" s="3"/>
+    </row>
+    <row r="2600" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2600" s="3" t="s">
+        <v>3982</v>
+      </c>
+      <c r="B2600" s="3" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C2600" s="3">
+        <v>537</v>
+      </c>
+      <c r="D2600" s="3">
+        <v>360943374</v>
+      </c>
+      <c r="E2600" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2600" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G2600" s="3"/>
+      <c r="H2600" s="3"/>
+      <c r="I2600" s="3"/>
+      <c r="J2600" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2600" s="3"/>
+      <c r="L2600" s="3"/>
+      <c r="M2600" s="3"/>
+    </row>
+    <row r="2601" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2601" s="3" t="s">
+        <v>3983</v>
+      </c>
+      <c r="B2601" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2601" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2601" s="3">
+        <v>360974791</v>
+      </c>
+      <c r="E2601" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2601" s="3" t="s">
+        <v>3984</v>
+      </c>
+      <c r="G2601" s="3"/>
+      <c r="H2601" s="3"/>
+      <c r="I2601" s="3"/>
+      <c r="J2601" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2601" s="3"/>
+      <c r="L2601" s="3"/>
+      <c r="M2601" s="3"/>
+    </row>
+    <row r="2602" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2602" s="3" t="s">
+        <v>3985</v>
+      </c>
+      <c r="B2602" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2602" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2602" s="3">
+        <v>361004062</v>
+      </c>
+      <c r="E2602" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2602" s="3" t="s">
+        <v>3986</v>
+      </c>
+      <c r="G2602" s="3"/>
+      <c r="H2602" s="3"/>
+      <c r="I2602" s="3"/>
+      <c r="J2602" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2602" s="3"/>
+      <c r="L2602" s="3"/>
+      <c r="M2602" s="3"/>
+    </row>
+    <row r="2603" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2603" s="3" t="s">
+        <v>3987</v>
+      </c>
+      <c r="B2603" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2603" s="3">
+        <v>536</v>
+      </c>
+      <c r="D2603" s="3">
+        <v>361008616</v>
+      </c>
+      <c r="E2603" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2603" s="3" t="s">
+        <v>3988</v>
+      </c>
+      <c r="G2603" s="3"/>
+      <c r="H2603" s="3"/>
+      <c r="I2603" s="3"/>
+      <c r="J2603" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2603" s="3"/>
+      <c r="L2603" s="3"/>
+      <c r="M2603" s="3"/>
+    </row>
+    <row r="2604" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2604" s="3" t="s">
+        <v>3989</v>
+      </c>
+      <c r="B2604" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2604" s="3">
+        <v>469</v>
+      </c>
+      <c r="D2604" s="3">
+        <v>361011620</v>
+      </c>
+      <c r="E2604" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2604" s="3" t="s">
+        <v>3990</v>
+      </c>
+      <c r="G2604" s="3"/>
+      <c r="H2604" s="3"/>
+      <c r="I2604" s="3"/>
+      <c r="J2604" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2604" s="3"/>
+      <c r="L2604" s="3"/>
+      <c r="M2604" s="3"/>
+    </row>
+    <row r="2605" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2605" s="3" t="s">
+        <v>3991</v>
+      </c>
+      <c r="B2605" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2605" s="3">
+        <v>556</v>
+      </c>
+      <c r="D2605" s="3">
+        <v>361022474</v>
+      </c>
+      <c r="E2605" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2605" s="3" t="s">
+        <v>3992</v>
+      </c>
+      <c r="G2605" s="3"/>
+      <c r="H2605" s="3"/>
+      <c r="I2605" s="3"/>
+      <c r="J2605" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2605" s="3"/>
+      <c r="L2605" s="3"/>
+      <c r="M2605" s="3"/>
+    </row>
+    <row r="2606" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2606" s="3" t="s">
+        <v>3993</v>
+      </c>
+      <c r="B2606" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2606" s="3">
+        <v>480</v>
+      </c>
+      <c r="D2606" s="3">
+        <v>361032552</v>
+      </c>
+      <c r="E2606" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2606" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="G2606" s="3"/>
+      <c r="H2606" s="3"/>
+      <c r="I2606" s="3"/>
+      <c r="J2606" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2606" s="3"/>
+      <c r="L2606" s="3"/>
+      <c r="M2606" s="3"/>
+    </row>
+    <row r="2607" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2607" s="3" t="s">
+        <v>3994</v>
+      </c>
+      <c r="B2607" s="3" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C2607" s="3">
+        <v>537</v>
+      </c>
+      <c r="D2607" s="3">
+        <v>361052331</v>
+      </c>
+      <c r="E2607" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2607" s="3" t="s">
+        <v>3995</v>
+      </c>
+      <c r="G2607" s="3"/>
+      <c r="H2607" s="3"/>
+      <c r="I2607" s="3"/>
+      <c r="J2607" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2607" s="3"/>
+      <c r="L2607" s="3"/>
+      <c r="M2607" s="3"/>
+    </row>
+    <row r="2608" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2608" s="3" t="s">
+        <v>3996</v>
+      </c>
+      <c r="B2608" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2608" s="3">
+        <v>473</v>
+      </c>
+      <c r="D2608" s="3">
+        <v>361053941</v>
+      </c>
+      <c r="E2608" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2608" s="3" t="s">
+        <v>3997</v>
+      </c>
+      <c r="G2608" s="3"/>
+      <c r="H2608" s="3"/>
+      <c r="I2608" s="3"/>
+      <c r="J2608" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2608" s="3"/>
+      <c r="L2608" s="3"/>
+      <c r="M2608" s="3"/>
+    </row>
+    <row r="2609" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2609" s="3" t="s">
+        <v>3998</v>
+      </c>
+      <c r="B2609" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2609" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2609" s="3">
+        <v>361057311</v>
+      </c>
+      <c r="E2609" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2609" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="G2609" s="3"/>
+      <c r="H2609" s="3"/>
+      <c r="I2609" s="3"/>
+      <c r="J2609" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2609" s="3"/>
+      <c r="L2609" s="3"/>
+      <c r="M2609" s="3"/>
+    </row>
+    <row r="2610" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2610" s="3" t="s">
+        <v>3999</v>
+      </c>
+      <c r="B2610" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2610" s="3">
+        <v>471</v>
+      </c>
+      <c r="D2610" s="3">
+        <v>361079010</v>
+      </c>
+      <c r="E2610" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2610" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G2610" s="3"/>
+      <c r="H2610" s="3"/>
+      <c r="I2610" s="3"/>
+      <c r="J2610" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2610" s="3"/>
+      <c r="L2610" s="3"/>
+      <c r="M2610" s="3"/>
+    </row>
+    <row r="2611" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2611" s="3" t="s">
+        <v>4000</v>
+      </c>
+      <c r="B2611" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2611" s="3">
+        <v>558</v>
+      </c>
+      <c r="D2611" s="3">
+        <v>361080619</v>
+      </c>
+      <c r="E2611" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2611" s="3" t="s">
+        <v>3453</v>
+      </c>
+      <c r="G2611" s="3"/>
+      <c r="H2611" s="3"/>
+      <c r="I2611" s="3"/>
+      <c r="J2611" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2611" s="3"/>
+      <c r="L2611" s="3"/>
+      <c r="M2611" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
